--- a/논문DB.xlsx
+++ b/논문DB.xlsx
@@ -10,12 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="논문" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="저자" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구자보정" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검색식" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연구자확인" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검색식" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'논문'!$A$1:$Q$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'저자'!$A$1:$G$892</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'연구자확인'!$A$1:$M$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,7 +43,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -68,6 +70,11 @@
         <fgColor rgb="00FFF4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B45309"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -81,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +98,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -647,6 +655,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -723,6 +732,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -806,6 +816,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -885,6 +896,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -964,6 +976,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1043,6 +1056,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1122,6 +1136,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1201,6 +1216,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1284,6 +1300,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1365,6 +1382,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1448,6 +1466,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1531,6 +1550,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1614,6 +1634,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1694,6 +1715,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1777,6 +1799,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1860,6 +1883,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1943,6 +1967,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -2019,6 +2044,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -2098,6 +2124,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2181,6 +2208,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -2261,6 +2289,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -2344,6 +2373,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24" ht="45" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -2427,6 +2457,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -2503,6 +2534,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26" ht="45" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2575,6 +2607,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2654,6 +2687,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2733,6 +2767,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -2816,6 +2851,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2899,6 +2935,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -2975,6 +3012,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -3058,6 +3096,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -3137,6 +3176,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -3217,6 +3257,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -3300,6 +3341,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -3383,6 +3425,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -3462,6 +3505,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38" ht="45" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3545,6 +3589,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39" ht="45" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -3628,6 +3673,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -3712,6 +3758,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41" ht="45" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
@@ -3796,6 +3843,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42" ht="45" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -3868,6 +3916,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43" ht="45" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -3951,6 +4000,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44" ht="45" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -4034,6 +4084,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -4113,6 +4164,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46" ht="45" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -4196,6 +4248,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -4279,6 +4332,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48" ht="45" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -4358,6 +4412,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49" ht="45" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -4441,6 +4496,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50" ht="45" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -4517,6 +4573,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51" ht="45" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -4600,6 +4657,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52" ht="45" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -4680,6 +4738,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53" ht="45" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -4766,6 +4825,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -4844,6 +4904,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55" ht="45" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -4927,6 +4988,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56" ht="45" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -5010,6 +5072,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -5086,6 +5149,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58" ht="45" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -5162,6 +5226,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59" ht="45" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -5245,6 +5310,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60" ht="45" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -5321,6 +5387,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61" ht="45" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -5397,6 +5464,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62" ht="45" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -5477,6 +5545,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63" ht="45" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -5557,6 +5626,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64" ht="45" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -5637,6 +5707,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -5717,6 +5788,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66" ht="45" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -5793,6 +5865,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67" ht="45" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -5876,6 +5949,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68" ht="45" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -5956,6 +6030,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69" ht="45" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -6039,6 +6114,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70" ht="45" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -6118,6 +6194,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71" ht="45" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
@@ -6201,6 +6278,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72" ht="45" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -6280,6 +6358,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -6356,6 +6435,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74" ht="45" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -6436,6 +6516,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75" ht="45" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -6519,6 +6600,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76" ht="45" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -6599,6 +6681,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77" ht="45" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -6682,6 +6765,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr"/>
     </row>
     <row r="78" ht="45" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -6765,6 +6849,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79" ht="45" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -6841,6 +6926,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80" ht="45" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -6920,6 +7006,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81" ht="45" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -7000,6 +7087,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82" ht="45" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -7083,6 +7171,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83" ht="45" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -7163,6 +7252,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84" ht="45" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -7246,6 +7336,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85" ht="45" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -7325,6 +7416,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86" ht="45" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -7404,6 +7496,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87" ht="45" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
@@ -7487,6 +7580,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88" ht="45" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -7566,6 +7660,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr"/>
     </row>
     <row r="89" ht="45" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -7644,6 +7739,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90" ht="45" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -7720,6 +7816,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91" ht="45" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
@@ -7803,6 +7900,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92" ht="45" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -7881,6 +7979,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93" ht="45" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -7964,6 +8063,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94" ht="45" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -8040,6 +8140,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95" ht="45" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -8119,6 +8220,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96" ht="45" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -8199,6 +8301,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97" ht="45" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -8278,6 +8381,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98" ht="45" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -8357,6 +8461,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99" ht="45" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
@@ -8440,6 +8545,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100" ht="45" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -8520,6 +8626,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101" ht="45" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
@@ -8599,6 +8706,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102" ht="45" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -8660,6 +8768,7 @@
           <t>2006-11-30</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" s="4" t="inlineStr">
         <is>
           <t>SETTING: The Korea Tuberculosis Surveillance (KTBS) network includes 248 health centres throughout the country, as well as other public and private health institutions.
@@ -8674,6 +8783,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103" ht="45" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
@@ -8735,6 +8845,7 @@
           <t>2003-03-08</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" s="4" t="inlineStr">
         <is>
           <t>OBJECTIVES: To establish a surveillance system for antituberculous drug resistance according to WHO and IUATLD guidelines, to collect the data of initial and acquired drug resistance, and to evaluate the efficacy of ongoing tuberculosis control strategies.
@@ -8748,6 +8859,7 @@
           <t>2026-09-30</t>
         </is>
       </c>
+      <c r="Q103" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q103"/>
@@ -9125,6 +9237,7 @@
           <t>Woo HJ</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Clinical Trial Center, Jeonbuk National University Hospital, Jeonju, Korea. / Nanum Space Co. Ltd, Jeonju, Korea.</t>
@@ -9157,6 +9270,7 @@
           <t>Kim MG</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Nanum Space Co. Ltd, Jeonju, Korea. / Department of Pharmacology, Jeonbuk National University Medical School, Jeonju, Korea.</t>
@@ -9189,6 +9303,7 @@
           <t>Kang G</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Department of Pharmacology, Chonnam National University Medical School, Hwasun, Korea. / Division of Clinical Pharmacology, Chonnam National University Hospital, Gwangju, Korea.</t>
@@ -9196,7 +9311,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chonnam National University Medical School</t>
+          <t>전남대학교</t>
         </is>
       </c>
     </row>
@@ -9221,6 +9336,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Kyungpook National University School of Medicine, Daegu, Korea.</t>
@@ -9253,6 +9369,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Busan, Korea.</t>
@@ -9285,6 +9402,7 @@
           <t>Choe YH</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Division of Respiratory Medicine and Allergy, Department of Internal Medicine, Jeonbuk National University Medical School, Jeonju, Korea.</t>
@@ -9317,6 +9435,7 @@
           <t>Kwon YS</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Chonnam National University Hospital, Chonnam National University Medical School, Gwangju, Korea. yskwon@jnu.ac.kr.</t>
@@ -9324,7 +9443,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chonnam National University Hospital</t>
+          <t>전남대학교병원</t>
         </is>
       </c>
     </row>
@@ -10570,6 +10689,7 @@
           <t>Kwak SH</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Republic of Korea.</t>
@@ -10602,6 +10722,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>Division of Health Policy and Management, Korea University College of Health Science, Seoul, Republic of Korea.</t>
@@ -10634,6 +10755,7 @@
           <t>Lee SW</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>Institute of Immunology and Immunological Diseases, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -10666,6 +10788,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University, Seoul, Republic of Korea.</t>
@@ -10698,6 +10821,7 @@
           <t>Sohn H</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University, Seoul, Republic of Korea.</t>
@@ -10730,6 +10854,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>Institute of Immunology and Immunological Diseases, Yonsei University College of Medicine, Seoul, Republic of Korea; Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea; Institute for Innovation in Digital Healthcare, Yonsei University, Seoul, Republic of Korea. Electronic address: mdkang@yuhs.ac.</t>
@@ -10762,6 +10887,7 @@
           <t>Hwang H</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Seoul National University College of Medicine, Seoul, South Korea. / Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul National University Bundang Hospital, Seongnam, South Korea.</t>
@@ -10794,6 +10920,7 @@
           <t>Shin JE</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Department of Nursing, Yonsei University Wonju College of Nursing, Wonju, South Korea.</t>
@@ -10826,6 +10953,7 @@
           <t>Seo S</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Korea Disease Control and Prevention Agency, Cheongju, South Korea.</t>
@@ -10858,6 +10986,7 @@
           <t>Hong SJ</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Korea Disease Control and Prevention Agency, Cheongju, South Korea.</t>
@@ -10890,6 +11019,7 @@
           <t>Jang MR</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Korea Disease Control and Prevention Agency, Cheongju, South Korea.</t>
@@ -10922,6 +11052,7 @@
           <t>Kang H</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Department of Chest Medicine, Masan National Tuberculosis Hospital, Masan, South Korea.</t>
@@ -10954,6 +11085,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Division of Pulmonology and Critical Care Medicine, Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Busan, South Korea.</t>
@@ -10986,6 +11118,7 @@
           <t>Kwon YS</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Chonnam National University Hospital, Chonnam National University Medical School, Gwangju, South Korea.</t>
@@ -10993,7 +11126,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chonnam National University Hospital</t>
+          <t>전남대학교병원</t>
         </is>
       </c>
     </row>
@@ -11018,6 +11151,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, South Korea.</t>
@@ -11050,6 +11184,7 @@
           <t>Shim TS</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, 88 Olympic-ro 43-gil, Songpa-gu, Seoul, 05505, South Korea. shimts@amc.seoul.kr.</t>
@@ -11082,6 +11217,7 @@
           <t>Yim JJ</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Seoul National University College of Medicine, Seoul, South Korea. yimjj@snu.ac.kr. / Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul National University Hospital, 101 Daehak-ro, Jongno-gu, Seoul, 03080, South Korea. yimjj@snu.ac.kr.</t>
@@ -11422,7 +11558,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hallym University Dongtan Sacred Heart Hospital</t>
+          <t>동탄성심병원</t>
         </is>
       </c>
     </row>
@@ -11484,6 +11620,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University, Seoul, Republic of Korea.</t>
@@ -11553,6 +11690,7 @@
           <t>Sohn H</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University, Seoul, Republic of Korea.</t>
@@ -11881,6 +12019,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -11913,6 +12052,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -11945,6 +12085,7 @@
           <t>Lee SW</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>Institute for Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, Korea.</t>
@@ -11977,6 +12118,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>Division of Health Policy and Management, Korea University College of Health Science, Seoul, Korea.</t>
@@ -12009,6 +12151,7 @@
           <t>Sohn H</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -12041,6 +12184,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -12073,6 +12217,7 @@
           <t>Lee H</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -12105,6 +12250,7 @@
           <t>Jeong H</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -12137,6 +12283,7 @@
           <t>Lee SE</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -12169,6 +12316,7 @@
           <t>Park YJ</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -12201,6 +12349,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>Department of Big Data Research and Development, National Health Insurance Service, Wonju, Korea.</t>
@@ -12233,6 +12382,7 @@
           <t>Kim EM</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>Department of Big Data Research and Development, National Health Insurance Service, Wonju, Korea.</t>
@@ -12265,6 +12415,7 @@
           <t>Koo M</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>Department of Big Data Research and Development, National Health Insurance Service, Wonju, Korea.</t>
@@ -12297,6 +12448,7 @@
           <t>Jang H</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>Department of Big Data Research and Development, National Health Insurance Service, Wonju, Korea.</t>
@@ -12329,6 +12481,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>Institute for Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, Korea. / Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Korea. / Institute for Innovation in Digital Healthcare, Yonsei University, Seoul, Korea.</t>
@@ -13365,6 +13518,8 @@
           <t>0000-0002-7178-5744</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13392,6 +13547,8 @@
           <t>0000-0001-8435-1403</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13419,6 +13576,8 @@
           <t>0000-0001-6912-8780</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13446,6 +13605,8 @@
           <t>0000-0002-4527-0368</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13473,6 +13634,8 @@
           <t>0009-0004-8650-5591</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15382,6 +15545,7 @@
           <t>Moon D</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, Busan, Republic of Korea.</t>
@@ -15451,6 +15615,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -15483,6 +15648,7 @@
           <t>Lee GI</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Republic of Korea.</t>
@@ -15552,6 +15718,7 @@
           <t>Jeon S</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>Graduate School of Public Health, Hanyang University, Seoul, Republic of Korea. / Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15584,6 +15751,7 @@
           <t>Lee JY</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15616,6 +15784,7 @@
           <t>Jeong I</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15648,6 +15817,7 @@
           <t>Sin S</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15680,6 +15850,7 @@
           <t>Lee I</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15712,6 +15883,7 @@
           <t>Kim Y</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15744,6 +15916,7 @@
           <t>Han AY</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15776,6 +15949,7 @@
           <t>Lee SE</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -15808,6 +15982,7 @@
           <t>Seo S</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -15840,6 +16015,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -15872,6 +16048,7 @@
           <t>Kwon Y</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -15904,6 +16081,7 @@
           <t>Song C</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -15936,6 +16114,7 @@
           <t>Joh JS</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul, Republic of Korea.</t>
@@ -15968,6 +16147,7 @@
           <t>Kim SH</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>Graduate School of Public Health, Hanyang University, Seoul, Republic of Korea. / Center for Global Health Practice, Institute of Health and Society, Hanyang University College of Medicine, Seoul, Republic of Korea.</t>
@@ -16308,7 +16488,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hallym University Dongtan Sacred Heart Hospital</t>
+          <t>동탄성심병원</t>
         </is>
       </c>
     </row>
@@ -16333,6 +16513,7 @@
           <t>Lee KN</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr"/>
       <c r="F211" t="inlineStr">
         <is>
           <t>Department of Statistics and Actuarial Science, Soongsil University, Seoul, Republic of Korea.</t>
@@ -16402,6 +16583,7 @@
           <t>Park J</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr">
         <is>
           <t>Center for Health Promotion, Samsung Medical Center, Sungkyunkwan University School of Medicine, Seoul, Republic of Korea.</t>
@@ -16508,6 +16690,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -16540,6 +16723,7 @@
           <t>Jeong Y</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Dankook University Hospital, Cheonan, Republic of Korea.</t>
@@ -16572,6 +16756,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr"/>
       <c r="F218" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Incheon, Republic of Korea.</t>
@@ -16604,6 +16789,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr"/>
       <c r="F219" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Incheon, Republic of Korea.</t>
@@ -16636,6 +16822,7 @@
           <t>Seo J</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>Team II, Research and Developement Center, The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -16668,6 +16855,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -16700,6 +16888,7 @@
           <t>Lee IH</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr"/>
       <c r="F222" t="inlineStr">
         <is>
           <t>Team II, Research and Developement Center, The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -16732,6 +16921,7 @@
           <t>Han J</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr"/>
       <c r="F223" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -16764,6 +16954,7 @@
           <t>Kwon Y</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr"/>
       <c r="F224" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -16796,6 +16987,7 @@
           <t>Shim E</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr"/>
       <c r="F225" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -16828,6 +17020,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr"/>
       <c r="F226" t="inlineStr">
         <is>
           <t>Division of Health Policy and Management, Korea University College of Health Science, Seoul, Korea.</t>
@@ -16860,6 +17053,7 @@
           <t>Kim G</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr"/>
       <c r="F227" t="inlineStr">
         <is>
           <t>Director for Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, 187, Osongsaengmyeong 2-ro, Osong-eup, Heungdeok-gu, Cheongju-si, Chungcheongbuk-do, 28159, Republic of Korea.</t>
@@ -16892,6 +17086,7 @@
           <t>Go U</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr"/>
       <c r="F228" t="inlineStr">
         <is>
           <t>Medical director of Infectious Disease Research Center, Department of Laboratory Medicine, Green Cross Laboratories, 107, Ihyeonro 30 beon-gil, Giheng-gu, Yongin-si, 16924 Gyeonggi-do, Republic of Korea.</t>
@@ -16924,6 +17119,7 @@
           <t>Park G</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr"/>
       <c r="F229" t="inlineStr">
         <is>
           <t>Director for Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, 187, Osongsaengmyeong 2-ro, Osong-eup, Heungdeok-gu, Cheongju-si, Chungcheongbuk-do, 28159, Republic of Korea.</t>
@@ -16956,6 +17152,7 @@
           <t>Kim Y</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr"/>
       <c r="F230" t="inlineStr">
         <is>
           <t>Director for Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, 187, Osongsaengmyeong 2-ro, Osong-eup, Heungdeok-gu, Cheongju-si, Chungcheongbuk-do, 28159, Republic of Korea.</t>
@@ -16988,6 +17185,7 @@
           <t>Jeong H</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>Director for Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, 187, Osongsaengmyeong 2-ro, Osong-eup, Heungdeok-gu, Cheongju-si, Chungcheongbuk-do, 28159, Republic of Korea.</t>
@@ -17020,6 +17218,7 @@
           <t>Park A</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr"/>
       <c r="F232" t="inlineStr">
         <is>
           <t>Director for Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, 187, Osongsaengmyeong 2-ro, Osong-eup, Heungdeok-gu, Cheongju-si, Chungcheongbuk-do, 28159, Republic of Korea.</t>
@@ -17052,6 +17251,7 @@
           <t>Park YJ</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr"/>
       <c r="F233" t="inlineStr">
         <is>
           <t>Director for Tuberculosis Policy, Department of Infectious Disease Policy, Korea Disease Control and Prevention Agency, 187, Osongsaengmyeong 2-ro, Osong-eup, Heungdeok-gu, Cheongju-si, Chungcheongbuk-do, 28159, Republic of Korea.</t>
@@ -17084,6 +17284,7 @@
           <t>Chung C</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr"/>
       <c r="F234" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Hallym University Dongtan Sacred Heart Hospital, Hallym University College of Medicine, Hwaseong, Republic of Korea.</t>
@@ -17091,7 +17292,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hallym University Dongtan Sacred Heart Hospital</t>
+          <t>동탄성심병원</t>
         </is>
       </c>
     </row>
@@ -17116,6 +17317,7 @@
           <t>Lee SW</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr"/>
       <c r="F235" t="inlineStr">
         <is>
           <t>Institute for Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -17148,6 +17350,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr"/>
       <c r="F236" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University, Seoul, Republic of Korea.</t>
@@ -17180,6 +17383,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr"/>
       <c r="F237" t="inlineStr">
         <is>
           <t>Division of Health Policy and Management, College of Health Science, Korea University, Seoul, Republic of Korea.</t>
@@ -17212,6 +17416,7 @@
           <t>Sohn H</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr"/>
       <c r="F238" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University, Seoul, Republic of Korea; Department of Human Systems Medicine, Seoul National University, Seoul, Republic of Korea; Institute of Health Policy and Management, Seoul National University, Seoul, Republic of Korea.</t>
@@ -17244,6 +17449,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, Republic of Korea. Electronic address: sooli10@hanmail.net.</t>
@@ -17276,6 +17482,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr"/>
       <c r="F240" t="inlineStr">
         <is>
           <t>Institute for Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, Republic of Korea; Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea. Electronic address: mdkang@yuhs.ac.</t>
@@ -17641,6 +17848,7 @@
           <t>Park S</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr"/>
       <c r="F250" t="inlineStr">
         <is>
           <t>Department of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Disease, National Institute of Health, Korea Disease Control and Prevention Agency, Cheongju-si, South Korea.</t>
@@ -17747,6 +17955,7 @@
           <t>Myong JP</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr"/>
       <c r="F253" t="inlineStr">
         <is>
           <t>Department of Occupational &amp; Environmental Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul 06591, Republic of Korea.</t>
@@ -17779,6 +17988,7 @@
           <t>Kim Y</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul 04564, Republic of Korea.</t>
@@ -17811,6 +18021,7 @@
           <t>Jeong I</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr"/>
       <c r="F255" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul 04564, Republic of Korea.</t>
@@ -17843,6 +18054,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul 04564, Republic of Korea.</t>
@@ -17875,6 +18087,7 @@
           <t>Sin S</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul 04564, Republic of Korea.</t>
@@ -17907,6 +18120,7 @@
           <t>Kwon Y</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr"/>
       <c r="F258" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju 28159, Republic of Korea.</t>
@@ -17939,6 +18153,7 @@
           <t>Song C</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr"/>
       <c r="F259" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju 28159, Republic of Korea.</t>
@@ -17971,6 +18186,7 @@
           <t>Joh JS</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr"/>
       <c r="F260" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, National Medical Center, Seoul 04564, Republic of Korea.</t>
@@ -18003,6 +18219,7 @@
           <t>Lee YH</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr"/>
       <c r="F261" t="inlineStr">
         <is>
           <t>Department of Occupational &amp; Environmental Medicine, College of Medicine, The Catholic University of Korea, Republic of Korea.</t>
@@ -18035,6 +18252,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr"/>
       <c r="F262" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -18067,6 +18285,7 @@
           <t>Park YJ</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -18099,6 +18318,7 @@
           <t>Kim G</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -18131,6 +18351,7 @@
           <t>Kim Y</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr"/>
       <c r="F265" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -18163,6 +18384,7 @@
           <t>Park G</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr"/>
       <c r="F266" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -18195,6 +18417,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea. Electronic address: jiongyou@naver.com.</t>
@@ -18227,6 +18450,7 @@
           <t>Myong JP</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr"/>
       <c r="F268" t="inlineStr">
         <is>
           <t>Department of Occupational &amp; Environmental Medicine, College of Medicine, The Catholic University of Korea, Republic of Korea. Electronic address: dr_mjp@naver.com.</t>
@@ -18259,6 +18483,7 @@
           <t>Lee H</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr"/>
       <c r="F269" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18291,6 +18516,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr"/>
       <c r="F270" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18323,6 +18549,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr"/>
       <c r="F271" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18355,6 +18582,7 @@
           <t>Park Y</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr"/>
       <c r="F272" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18387,6 +18615,7 @@
           <t>Shin J</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr"/>
       <c r="F273" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18419,6 +18648,7 @@
           <t>Cho G</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr"/>
       <c r="F274" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18451,6 +18681,7 @@
           <t>Park S</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18483,6 +18714,7 @@
           <t>Jang A</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr"/>
       <c r="F276" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18515,6 +18747,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr"/>
       <c r="F277" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18547,6 +18780,7 @@
           <t>Kim Y</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr"/>
       <c r="F278" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18579,6 +18813,7 @@
           <t>Kim G</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18611,6 +18846,7 @@
           <t>Park G</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18643,6 +18879,7 @@
           <t>Kwon S</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr"/>
       <c r="F281" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18675,6 +18912,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E282" t="inlineStr"/>
       <c r="F282" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18707,6 +18945,7 @@
           <t>Choi B</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr"/>
       <c r="F283" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18739,6 +18978,7 @@
           <t>You S</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr"/>
       <c r="F284" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18771,6 +19011,7 @@
           <t>Seo S</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr"/>
       <c r="F285" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18803,6 +19044,7 @@
           <t>Song C</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr"/>
       <c r="F286" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18835,6 +19077,7 @@
           <t>Han J</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr"/>
       <c r="F287" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18867,6 +19110,7 @@
           <t>Han H</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr"/>
       <c r="F288" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18899,6 +19143,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr"/>
       <c r="F289" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18931,6 +19176,7 @@
           <t>Jang M</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr"/>
       <c r="F290" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18963,6 +19209,7 @@
           <t>Shim J</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr"/>
       <c r="F291" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -18995,6 +19242,7 @@
           <t>Choi S</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr"/>
       <c r="F292" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19027,6 +19275,7 @@
           <t>Jeong H</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr"/>
       <c r="F293" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19059,6 +19308,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E294" t="inlineStr"/>
       <c r="F294" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19091,6 +19341,7 @@
           <t>Han S</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr"/>
       <c r="F295" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19123,6 +19374,7 @@
           <t>Park Y</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr"/>
       <c r="F296" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19155,6 +19407,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr"/>
       <c r="F297" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19187,6 +19440,7 @@
           <t>In H</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr"/>
       <c r="F298" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19219,6 +19473,7 @@
           <t>Park G</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr"/>
       <c r="F299" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19251,6 +19506,7 @@
           <t>Oh S</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr"/>
       <c r="F300" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19283,6 +19539,7 @@
           <t>Park A</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr"/>
       <c r="F301" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19315,6 +19572,7 @@
           <t>Park J</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr"/>
       <c r="F302" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19347,6 +19605,7 @@
           <t>Kim S</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19379,6 +19638,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr"/>
       <c r="F304" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19411,6 +19671,7 @@
           <t>Park Y</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr"/>
       <c r="F305" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19443,6 +19704,7 @@
           <t>Lee H</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr"/>
       <c r="F306" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19475,6 +19737,7 @@
           <t>Koo I</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr"/>
       <c r="F307" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -19507,6 +19770,7 @@
           <t>Yoo J</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr"/>
       <c r="F308" t="inlineStr">
         <is>
           <t>질병관리청 진단분석국 세균분석과.</t>
@@ -19539,6 +19803,7 @@
           <t>Kim Y</t>
         </is>
       </c>
+      <c r="E309" t="inlineStr"/>
       <c r="F309" t="inlineStr">
         <is>
           <t>질병관리청 진단분석국 세균분석과.</t>
@@ -19571,6 +19836,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr"/>
       <c r="F310" t="inlineStr">
         <is>
           <t>질병관리청 진단분석국 세균분석과.</t>
@@ -19603,6 +19869,7 @@
           <t>Lee M</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>질병관리청 진단분석국 세균분석과.</t>
@@ -19635,6 +19902,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr"/>
       <c r="F312" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -19667,6 +19935,7 @@
           <t>Ko Y</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr"/>
       <c r="F313" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Kangdong Sacred Heart Hospital, College of Medicine, Hallym University, Seoul, Republic of Korea.</t>
@@ -19699,6 +19968,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr"/>
       <c r="F314" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Incheon, Republic of Korea.</t>
@@ -19731,6 +20001,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Inje University Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -19763,6 +20034,7 @@
           <t>Oh JY</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy, and Critical Care Medicine, Department of Internal Medicine, Korea University Guro Hospital, Korea University College of Medicine, Seoul, Republic of Korea.</t>
@@ -19795,6 +20067,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E317" t="inlineStr"/>
       <c r="F317" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, Republic of Korea.</t>
@@ -19827,6 +20100,7 @@
           <t>Lee T</t>
         </is>
       </c>
+      <c r="E318" t="inlineStr"/>
       <c r="F318" t="inlineStr">
         <is>
           <t>Division of Respiratory and Critical Care Medicine, Department of Internal Medicine, Ulsan University Hospital, University of Ulsan College of Medicine, Ulsan, Republic of Korea.</t>
@@ -19859,6 +20133,7 @@
           <t>Kim YC</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr"/>
       <c r="F319" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Chonnam National University Hwasun Hospital, Chonnam National University Medical School, Hwasun, Republic of Korea.</t>
@@ -19866,7 +20141,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Chonnam National University Hwasun Hospital</t>
+          <t>화순전남대학교병원</t>
         </is>
       </c>
     </row>
@@ -19891,6 +20166,7 @@
           <t>Lim SC</t>
         </is>
       </c>
+      <c r="E320" t="inlineStr"/>
       <c r="F320" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Chonnam National University Medical School, Gwangju, Republic of Korea.</t>
@@ -19898,7 +20174,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Chonnam National University Medical School</t>
+          <t>전남대학교</t>
         </is>
       </c>
     </row>
@@ -19923,6 +20199,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr"/>
       <c r="F321" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Inje University Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -19955,6 +20232,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E322" t="inlineStr"/>
       <c r="F322" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Republic of Korea.</t>
@@ -19987,6 +20265,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E323" t="inlineStr"/>
       <c r="F323" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Incheon, Republic of Korea.</t>
@@ -20463,6 +20742,7 @@
           <t>Lee HY</t>
         </is>
       </c>
+      <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -20495,6 +20775,7 @@
           <t>Kwon Y</t>
         </is>
       </c>
+      <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -20527,6 +20808,7 @@
           <t>Lee SE</t>
         </is>
       </c>
+      <c r="E338" t="inlineStr"/>
       <c r="F338" t="inlineStr">
         <is>
           <t>Epidemiological Investigation Team, Central Disaster Safety and Countermeasure Headquarters, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -20559,6 +20841,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -20591,6 +20874,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E340" t="inlineStr"/>
       <c r="F340" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Policy, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -20623,6 +20907,7 @@
           <t>Son E</t>
         </is>
       </c>
+      <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, Korea.</t>
@@ -20655,6 +20940,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E342" t="inlineStr"/>
       <c r="F342" t="inlineStr">
         <is>
           <t>Division of Health Policy and Management, Korea University College of Health Science, Seoul, Korea.</t>
@@ -20687,6 +20973,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Busan, Korea.</t>
@@ -20719,6 +21006,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Korea.</t>
@@ -20751,6 +21039,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E345" t="inlineStr"/>
       <c r="F345" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -20783,6 +21072,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, Korea.</t>
@@ -20852,6 +21142,7 @@
           <t>Kim IK</t>
         </is>
       </c>
+      <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr">
         <is>
           <t>Division of Infectious Disease Response, Capital Regional Center for Disease Control and Prevention, Korea Disease Control and Prevention Agency, Seoul, Republic of Korea.</t>
@@ -20884,6 +21175,7 @@
           <t>Kim SJ</t>
         </is>
       </c>
+      <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr">
         <is>
           <t>Division of Infectious Disease Response, Capital Regional Center for Disease Control and Prevention, Korea Disease Control and Prevention Agency, Seoul, Republic of Korea.</t>
@@ -20916,6 +21208,7 @@
           <t>Kim HS</t>
         </is>
       </c>
+      <c r="E350" t="inlineStr"/>
       <c r="F350" t="inlineStr">
         <is>
           <t>Division of Infectious Disease Response, Capital Regional Center for Disease Control and Prevention, Korea Disease Control and Prevention Agency, Seoul, Republic of Korea.</t>
@@ -21614,6 +21907,7 @@
           <t>Lee H</t>
         </is>
       </c>
+      <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr">
         <is>
           <t>School of Pharmacy, Sungkyunkwan University, Suwon, South Korea; Department of Biohealth Regulatory Science, Sungkyunkwan University, Suwon, South Korea.</t>
@@ -21646,6 +21940,7 @@
           <t>Bea S</t>
         </is>
       </c>
+      <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr">
         <is>
           <t>School of Pharmacy, Sungkyunkwan University, Suwon, South Korea; Division of Pharmacoepidemiology and Pharmacoeconomics, Department of Medicine, Brigham and Women's Hospital and Harvard Medical School, Boston, Massachusetts, USA.</t>
@@ -21678,6 +21973,7 @@
           <t>Kim JH</t>
         </is>
       </c>
+      <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr">
         <is>
           <t>School of Pharmacy, Sungkyunkwan University, Suwon, South Korea; Department of Biohealth Regulatory Science, Sungkyunkwan University, Suwon, South Korea.</t>
@@ -21710,6 +22006,7 @@
           <t>Jeong HE</t>
         </is>
       </c>
+      <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr">
         <is>
           <t>School of Pharmacy, Sungkyunkwan University, Suwon, South Korea; Department of Biohealth Regulatory Science, Sungkyunkwan University, Suwon, South Korea.</t>
@@ -21742,6 +22039,7 @@
           <t>Jang SH</t>
         </is>
       </c>
+      <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy, and Critical Care Medicine, College of Medicine, Hallym University Sacred Heart Hospital, Hallym University College of Medicine, Anyang, South Korea.</t>
@@ -21774,6 +22072,7 @@
           <t>Son H</t>
         </is>
       </c>
+      <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, College of Medicine, Dong-A University, Busan, South Korea.</t>
@@ -21806,6 +22105,7 @@
           <t>Shin JY</t>
         </is>
       </c>
+      <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr">
         <is>
           <t>School of Pharmacy, Sungkyunkwan University, Suwon, South Korea; Department of Biohealth Regulatory Science, Sungkyunkwan University, Suwon, South Korea; Samsung Advanced Institute for Health Sciences &amp; Technology, Sungkyunkwan University, Seoul, South Korea. Electronic address: shin.jy@skku.edu.</t>
@@ -21838,6 +22138,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -21870,6 +22171,7 @@
           <t>Jeong Y</t>
         </is>
       </c>
+      <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Dankook University Hospital, Cheonan, Republic of Korea.</t>
@@ -21902,6 +22204,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E378" t="inlineStr"/>
       <c r="F378" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -21934,6 +22237,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -21966,6 +22270,7 @@
           <t>Chung E</t>
         </is>
       </c>
+      <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Korea.</t>
@@ -21998,6 +22303,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -22030,6 +22336,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Busan, Korea.</t>
@@ -22062,6 +22369,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, Korea.</t>
@@ -22094,6 +22402,7 @@
           <t>Kang HY</t>
         </is>
       </c>
+      <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr">
         <is>
           <t>Department of Cancer Control and Population Health, National Cancer Center Graduate School of Cancer Science and Policy, Goyang, Korea.</t>
@@ -22126,6 +22435,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr">
         <is>
           <t>Jeju Double Cross Clinic, Korean National Tuberculosis Association, Jeju, Korea.</t>
@@ -22158,6 +22468,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr">
         <is>
           <t>Department of Health Policy Research, National Evidence-Based Healthcare Collaborating Agency, Seoul, Korea.</t>
@@ -22190,6 +22501,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E387" t="inlineStr"/>
       <c r="F387" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Konyang University College of Medicine, Daejeon, Korea.</t>
@@ -22222,6 +22534,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Korea. / Institute of Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, Korea.</t>
@@ -22254,6 +22567,7 @@
           <t>Yu S</t>
         </is>
       </c>
+      <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr">
         <is>
           <t>School of Health Policy and Management, College of Health Science, Korea University, Seoul, Republic of Korea. / BK21 FOUR R&amp;E Center for Learning Health Systems, Korea University, Seoul, Republic of Korea.</t>
@@ -22286,6 +22600,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E390" t="inlineStr"/>
       <c r="F390" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University, Seoul, Republic of Korea.</t>
@@ -22318,6 +22633,7 @@
           <t>Kang HY</t>
         </is>
       </c>
+      <c r="E391" t="inlineStr"/>
       <c r="F391" t="inlineStr">
         <is>
           <t>Department of Cancer Control and Population Health, National Cancer Center Graduate School of Cancer Science and Policy, Goyang, Republic of Korea.</t>
@@ -22350,6 +22666,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea. / Institute for Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22382,6 +22699,7 @@
           <t>Lee GI</t>
         </is>
       </c>
+      <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr">
         <is>
           <t>The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Republic of Korea.</t>
@@ -22451,6 +22769,7 @@
           <t>Hyun J</t>
         </is>
       </c>
+      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
           <t>Division of Infectious Diseases, Department of Internal Medicine, Inje University Ilsan Paik Hospital, Goyang, Republic of Korea. / Department of Internal Medicine, Yonsei University College of Medicine, Seoul, South Korea.</t>
@@ -22483,6 +22802,7 @@
           <t>Lee M</t>
         </is>
       </c>
+      <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr">
         <is>
           <t>Department of Biomedical Systems Informatics, Biostatistics Collaboration Unit, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22515,6 +22835,7 @@
           <t>Jung I</t>
         </is>
       </c>
+      <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr">
         <is>
           <t>Division of Biostatistics, Department of Biomedical Systems Informatics, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22547,6 +22868,7 @@
           <t>Kim E</t>
         </is>
       </c>
+      <c r="E398" t="inlineStr"/>
       <c r="F398" t="inlineStr">
         <is>
           <t>Department of Biomedical Systems Informatics, Biostatistics Collaboration Unit, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22579,6 +22901,7 @@
           <t>Hahn SM</t>
         </is>
       </c>
+      <c r="E399" t="inlineStr"/>
       <c r="F399" t="inlineStr">
         <is>
           <t>Department of Pediatric Hematology-Oncology, Yonsei Cancer Center, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22611,6 +22934,7 @@
           <t>Kim YR</t>
         </is>
       </c>
+      <c r="E400" t="inlineStr"/>
       <c r="F400" t="inlineStr">
         <is>
           <t>Division of Hematology, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22643,6 +22967,7 @@
           <t>Lim S</t>
         </is>
       </c>
+      <c r="E401" t="inlineStr"/>
       <c r="F401" t="inlineStr">
         <is>
           <t>Department of Pediatrics, Severance Children's Hospital, Yonsei University College of Medicine, 50-1 Yonsei-Ro, Seodaemun-Gu, Seoul, 03722, Republic of Korea.</t>
@@ -22675,6 +23000,7 @@
           <t>Ihn K</t>
         </is>
       </c>
+      <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
           <t>Department of Pediatric Surgery, Department of Surgery, Severance Children's Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22707,6 +23033,7 @@
           <t>Kim MY</t>
         </is>
       </c>
+      <c r="E403" t="inlineStr"/>
       <c r="F403" t="inlineStr">
         <is>
           <t>Department of Pediatrics, Severance Children's Hospital, Yonsei University College of Medicine, 50-1 Yonsei-Ro, Seodaemun-Gu, Seoul, 03722, Republic of Korea. / Institute for Immunology and Immunological Diseases, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22739,6 +23066,7 @@
           <t>Ahn JG</t>
         </is>
       </c>
+      <c r="E404" t="inlineStr"/>
       <c r="F404" t="inlineStr">
         <is>
           <t>Department of Pediatrics, Severance Children's Hospital, Yonsei University College of Medicine, 50-1 Yonsei-Ro, Seodaemun-Gu, Seoul, 03722, Republic of Korea. / Institute for Immunology and Immunological Diseases, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -22771,6 +23099,7 @@
           <t>Yeom JS</t>
         </is>
       </c>
+      <c r="E405" t="inlineStr"/>
       <c r="F405" t="inlineStr">
         <is>
           <t>Division of Infectious Disease, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, 50-1 Yonsei-Ro Seodaemun-Gu, Seoul, 03722, Republic of Korea.</t>
@@ -22803,6 +23132,7 @@
           <t>Jeong SJ</t>
         </is>
       </c>
+      <c r="E406" t="inlineStr"/>
       <c r="F406" t="inlineStr">
         <is>
           <t>Division of Infectious Disease, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, 50-1 Yonsei-Ro Seodaemun-Gu, Seoul, 03722, Republic of Korea. JSJ@yuhs.ac.</t>
@@ -22835,6 +23165,7 @@
           <t>Kang JM</t>
         </is>
       </c>
+      <c r="E407" t="inlineStr"/>
       <c r="F407" t="inlineStr">
         <is>
           <t>Department of Pediatrics, Severance Children's Hospital, Yonsei University College of Medicine, 50-1 Yonsei-Ro, Seodaemun-Gu, Seoul, 03722, Republic of Korea. umi87c@yuhs.ac. / Institute for Immunology and Immunological Diseases, Yonsei University College of Medicine, Seoul, Republic of Korea. umi87c@yuhs.ac.</t>
@@ -22867,6 +23198,7 @@
           <t>Jeong YJ</t>
         </is>
       </c>
+      <c r="E408" t="inlineStr"/>
       <c r="F408" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Dongguk University Ilsan Hospital, Goyang, Republic of Korea.</t>
@@ -22899,6 +23231,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Republic of Korea.</t>
@@ -22931,6 +23264,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -22963,6 +23297,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -22995,6 +23330,7 @@
           <t>Ko Y</t>
         </is>
       </c>
+      <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Kangdong Sacred Heart Hospital, Hallym University College of Medicine, Seoul, Republic of Korea.</t>
@@ -23027,6 +23363,7 @@
           <t>Oh JY</t>
         </is>
       </c>
+      <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Korea University Guro Hospital, Korea University College of Medicine, Seoul, Republic of Korea.</t>
@@ -23059,6 +23396,7 @@
           <t>Lee EH</t>
         </is>
       </c>
+      <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -23091,6 +23429,7 @@
           <t>Yang B</t>
         </is>
       </c>
+      <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Chungbuk National University Hospital, Chungbuk National University College of Medicine, Cheongju, Republic of Korea.</t>
@@ -23123,6 +23462,7 @@
           <t>Ahn JH</t>
         </is>
       </c>
+      <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -23155,6 +23495,7 @@
           <t>Kim JW</t>
         </is>
       </c>
+      <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Uijeongbu St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Uijeongbu, Republic of Korea.</t>
@@ -23187,6 +23528,7 @@
           <t>Hwang YI</t>
         </is>
       </c>
+      <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr">
         <is>
           <t>Department of Pulmonary, Allergy and Critical Care Medicine, Hallym University Sacred Heart Hospital, Anyang, Republic of Korea.</t>
@@ -23219,6 +23561,7 @@
           <t>Park KJ</t>
         </is>
       </c>
+      <c r="E419" t="inlineStr"/>
       <c r="F419" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, Ajou University School of Medicine, Suwon, Republic of Korea.</t>
@@ -23251,6 +23594,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E420" t="inlineStr"/>
       <c r="F420" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -23283,6 +23627,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E421" t="inlineStr"/>
       <c r="F421" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -23315,6 +23660,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E422" t="inlineStr"/>
       <c r="F422" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -23347,6 +23693,7 @@
           <t>Ki MS</t>
         </is>
       </c>
+      <c r="E423" t="inlineStr"/>
       <c r="F423" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Yonsei University College of Medicine, Seoul, Korea.</t>
@@ -23379,6 +23726,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E424" t="inlineStr"/>
       <c r="F424" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -23448,6 +23796,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E426" t="inlineStr"/>
       <c r="F426" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Konyang University College of Medicine, Daejeon, Korea.</t>
@@ -23480,6 +23829,7 @@
           <t>Sohn H</t>
         </is>
       </c>
+      <c r="E427" t="inlineStr"/>
       <c r="F427" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -23845,6 +24195,7 @@
           <t>Jeong YJ</t>
         </is>
       </c>
+      <c r="E437" t="inlineStr"/>
       <c r="F437" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Dongguk University Ilsan Hospital, Goyang, Republic of Korea.</t>
@@ -23877,6 +24228,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E438" t="inlineStr"/>
       <c r="F438" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Republic of Korea.</t>
@@ -23909,6 +24261,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E439" t="inlineStr"/>
       <c r="F439" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -23941,6 +24294,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E440" t="inlineStr"/>
       <c r="F440" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -23973,6 +24327,7 @@
           <t>Ko Y</t>
         </is>
       </c>
+      <c r="E441" t="inlineStr"/>
       <c r="F441" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Kangdong Sacred Heart Hospital, Hallym University College of Medicine, Seoul, Republic of Korea.</t>
@@ -24005,6 +24360,7 @@
           <t>Oh JY</t>
         </is>
       </c>
+      <c r="E442" t="inlineStr"/>
       <c r="F442" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy, and Critical Care Medicine, Department of Internal Medicine, Korea University Guro Hospital, Korea University College of Medicine, Seoul, Republic of Korea.</t>
@@ -24037,6 +24393,7 @@
           <t>Lee EH</t>
         </is>
       </c>
+      <c r="E443" t="inlineStr"/>
       <c r="F443" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -24069,6 +24426,7 @@
           <t>Yang B</t>
         </is>
       </c>
+      <c r="E444" t="inlineStr"/>
       <c r="F444" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Chungbuk National University Hospital, Chungbuk National University College of Medicine, Cheongju, Republic of Korea.</t>
@@ -24101,6 +24459,7 @@
           <t>Lee MK</t>
         </is>
       </c>
+      <c r="E445" t="inlineStr"/>
       <c r="F445" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Busan, Republic of Korea.</t>
@@ -24133,6 +24492,7 @@
           <t>Kim YS</t>
         </is>
       </c>
+      <c r="E446" t="inlineStr"/>
       <c r="F446" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, School of Medicine, Pusan National University Yangsan Hospital, Pusan National University and Research Institute of Convergence Biomedical Science and Technology, Busan, Republic of Korea.</t>
@@ -24165,6 +24525,7 @@
           <t>Chang JH</t>
         </is>
       </c>
+      <c r="E447" t="inlineStr"/>
       <c r="F447" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Mokdong Hospital, Ewha Women's University, Seoul, Republic of Korea.</t>
@@ -24172,7 +24533,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Mokdong Hospital</t>
+          <t>이대목동병원</t>
         </is>
       </c>
     </row>
@@ -24197,6 +24558,7 @@
           <t>Jegal Y</t>
         </is>
       </c>
+      <c r="E448" t="inlineStr"/>
       <c r="F448" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Department of Internal Medicine, Ulsan University Hospital, University of Ulsan College of Medicine, Ulsan, Republic of Korea.</t>
@@ -24229,6 +24591,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E449" t="inlineStr"/>
       <c r="F449" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -24261,6 +24624,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E450" t="inlineStr"/>
       <c r="F450" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -24293,6 +24657,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E451" t="inlineStr"/>
       <c r="F451" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -24399,6 +24764,7 @@
           <t>Lim NR</t>
         </is>
       </c>
+      <c r="E454" t="inlineStr"/>
       <c r="F454" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Korea National Institute of Health, Korea Disease Control and Prevention Agency, Cheongju-si 28159, Republic of Korea.</t>
@@ -24468,6 +24834,7 @@
           <t>Jung J</t>
         </is>
       </c>
+      <c r="E456" t="inlineStr"/>
       <c r="F456" t="inlineStr">
         <is>
           <t>Clinical Research Center, Masan National Tuberculosis Hospital, Changwon-si 51755, Republic of Korea.</t>
@@ -24500,6 +24867,7 @@
           <t>Sung N</t>
         </is>
       </c>
+      <c r="E457" t="inlineStr"/>
       <c r="F457" t="inlineStr">
         <is>
           <t>Clinical Research Center, Masan National Tuberculosis Hospital, Changwon-si 51755, Republic of Korea.</t>
@@ -24532,6 +24900,7 @@
           <t>Kim S</t>
         </is>
       </c>
+      <c r="E458" t="inlineStr"/>
       <c r="F458" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Korea National Institute of Health, Korea Disease Control and Prevention Agency, Cheongju-si 28159, Republic of Korea.</t>
@@ -24564,6 +24933,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E459" t="inlineStr"/>
       <c r="F459" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Konyang University College of Medicine, Daejeon, South Korea.</t>
@@ -24596,6 +24966,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E460" t="inlineStr"/>
       <c r="F460" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Busan, South Korea.</t>
@@ -24813,6 +25184,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E466" t="inlineStr"/>
       <c r="F466" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, South Korea.</t>
@@ -24845,6 +25217,7 @@
           <t>Lee H</t>
         </is>
       </c>
+      <c r="E467" t="inlineStr"/>
       <c r="F467" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -24877,6 +25250,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E468" t="inlineStr"/>
       <c r="F468" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -24909,6 +25283,7 @@
           <t>Park G</t>
         </is>
       </c>
+      <c r="E469" t="inlineStr"/>
       <c r="F469" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -24941,6 +25316,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E470" t="inlineStr"/>
       <c r="F470" t="inlineStr">
         <is>
           <t>질병관리청 감염병정책국 결핵정책과.</t>
@@ -24973,6 +25349,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E471" t="inlineStr"/>
       <c r="F471" t="inlineStr">
         <is>
           <t>Research and Development Center, Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, South Korea.</t>
@@ -25005,6 +25382,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E472" t="inlineStr"/>
       <c r="F472" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Busan, South Korea.</t>
@@ -25037,6 +25415,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Pusan National University School of Medicine, Yangsan, South Korea.</t>
@@ -25106,6 +25485,7 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr">
         <is>
           <t>Central Training Institute, Korean National Tuberculosis Association, Seoul, South Korea.</t>
@@ -25138,6 +25518,7 @@
           <t>Kim HS</t>
         </is>
       </c>
+      <c r="E476" t="inlineStr"/>
       <c r="F476" t="inlineStr">
         <is>
           <t>Office of Policy Research for Future Healthcare, National Evidence-Based Healthcare Collaborating Agency, Jung-gu, Seoul, South Korea.</t>
@@ -25170,6 +25551,7 @@
           <t>Seo JM</t>
         </is>
       </c>
+      <c r="E477" t="inlineStr"/>
       <c r="F477" t="inlineStr">
         <is>
           <t>Research and Development Center, Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, South Korea.</t>
@@ -25276,6 +25658,7 @@
           <t>Teo AKJ</t>
         </is>
       </c>
+      <c r="E480" t="inlineStr"/>
       <c r="F480" t="inlineStr">
         <is>
           <t>Saw Swee Hock School of Public Health, National University of Singapore and National University Health System, Singapore, Singapore. / Faculty of Medicine and Health, University of Sydney, Sydney, NSW, Australia. / The University of Sydney Institute for Infectious Diseases (Sydney ID) and the Centre of Research Excellence in Tuberculosis (TB-CRE), Sydney, NSW, Australia.</t>
@@ -25308,6 +25691,7 @@
           <t>Rahevar K</t>
         </is>
       </c>
+      <c r="E481" t="inlineStr"/>
       <c r="F481" t="inlineStr">
         <is>
           <t>World Health Organization, Regional Office for the Western Pacific, Manila, Philippines. rahevark@who.int.</t>
@@ -25340,6 +25724,7 @@
           <t>Morishita F</t>
         </is>
       </c>
+      <c r="E482" t="inlineStr"/>
       <c r="F482" t="inlineStr">
         <is>
           <t>World Health Organization, Regional Office for the Western Pacific, Manila, Philippines.</t>
@@ -25372,6 +25757,7 @@
           <t>Ang A</t>
         </is>
       </c>
+      <c r="E483" t="inlineStr"/>
       <c r="F483" t="inlineStr">
         <is>
           <t>Division of Infectious Diseases, Department of Medicine, Woodlands Health, Singapore, Singapore.</t>
@@ -25404,6 +25790,7 @@
           <t>Yoshiyama T</t>
         </is>
       </c>
+      <c r="E484" t="inlineStr"/>
       <c r="F484" t="inlineStr">
         <is>
           <t>Research Institute of Tuberculosis, Anti-Tuberculosis Association, Tokyo, Japan.</t>
@@ -25436,6 +25823,7 @@
           <t>Ohkado A</t>
         </is>
       </c>
+      <c r="E485" t="inlineStr"/>
       <c r="F485" t="inlineStr">
         <is>
           <t>Research Institute of Tuberculosis, Anti-Tuberculosis Association, Tokyo, Japan.</t>
@@ -25468,6 +25856,7 @@
           <t>Kawatsu L</t>
         </is>
       </c>
+      <c r="E486" t="inlineStr"/>
       <c r="F486" t="inlineStr">
         <is>
           <t>Research Institute of Tuberculosis, Anti-Tuberculosis Association, Tokyo, Japan.</t>
@@ -25500,6 +25889,7 @@
           <t>Yamada N</t>
         </is>
       </c>
+      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
           <t>Research Institute of Tuberculosis, Anti-Tuberculosis Association, Tokyo, Japan.</t>
@@ -25532,6 +25922,7 @@
           <t>Uchimura K</t>
         </is>
       </c>
+      <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
           <t>Research Institute of Tuberculosis, Anti-Tuberculosis Association, Tokyo, Japan.</t>
@@ -25564,6 +25955,7 @@
           <t>Choi Y</t>
         </is>
       </c>
+      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
           <t>Korean National Tuberculosis Association, Seoul, Republic of Korea.</t>
@@ -25596,6 +25988,7 @@
           <t>Chen Z</t>
         </is>
       </c>
+      <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
           <t>Office of International Cooperation, Innovation Alliance on Tuberculosis Diagnosis and Treatment, Beijing, China.</t>
@@ -25628,6 +26021,7 @@
           <t>Yi S</t>
         </is>
       </c>
+      <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
           <t>Saw Swee Hock School of Public Health, National University of Singapore and National University Health System, Singapore, Singapore. / KHANA Center for Population Health Research, Phnom Penh, Cambodia. / Center for Global Health Research, Public Health Program, Touro University California, Vallejo, CA, USA.</t>
@@ -25660,6 +26054,7 @@
           <t>Yanagawa M</t>
         </is>
       </c>
+      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
           <t>World Health Organization, Regional Office for the Western Pacific, Manila, Philippines.</t>
@@ -25692,6 +26087,7 @@
           <t>Oh KH</t>
         </is>
       </c>
+      <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
           <t>World Health Organization, Regional Office for the Western Pacific, Manila, Philippines.</t>
@@ -25724,6 +26120,7 @@
           <t>Viney K</t>
         </is>
       </c>
+      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
           <t>Global Tuberculosis Programme, World Health Organization, Geneva, Switzerland.</t>
@@ -25756,6 +26153,7 @@
           <t>Marais B</t>
         </is>
       </c>
+      <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
           <t>Faculty of Medicine and Health, University of Sydney, Sydney, NSW, Australia. / The University of Sydney Institute for Infectious Diseases (Sydney ID) and the Centre of Research Excellence in Tuberculosis (TB-CRE), Sydney, NSW, Australia.</t>
@@ -25788,6 +26186,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
           <t>Korean National Tuberculosis Association, Seoul, Republic of Korea.</t>
@@ -25820,6 +26219,7 @@
           <t>Kato S</t>
         </is>
       </c>
+      <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
           <t>Research Institute of Tuberculosis, Anti-Tuberculosis Association, Tokyo, Japan.</t>
@@ -25852,6 +26252,7 @@
           <t>Liu Y</t>
         </is>
       </c>
+      <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
           <t>Beijing Chest Hospital, Capital Medical University, Beijing, China.</t>
@@ -25884,6 +26285,7 @@
           <t>Ong CWM</t>
         </is>
       </c>
+      <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
           <t>Division of Infectious Diseases, Department of Medicine, National University Hospital, Singapore, Singapore. / Infectious Diseases Translational Research Programme, Department of Medicine, National University of Singapore, Singapore, Singapore. / Institute of Health Innovation and Technology (iHealthtech), National University of Singapore, Singapore, Singapore.</t>
@@ -25916,6 +26318,7 @@
           <t>Islam T</t>
         </is>
       </c>
+      <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
           <t>World Health Organization, Regional Office for the Western Pacific, Manila, Philippines.</t>
@@ -26244,6 +26647,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, College of Medicine, Incheon St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26276,6 +26680,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, College of Medicine, Seoul St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26308,6 +26713,7 @@
           <t>Choi JY</t>
         </is>
       </c>
+      <c r="E511" t="inlineStr"/>
       <c r="F511" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, College of Medicine, Incheon St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26340,6 +26746,7 @@
           <t>Shin AY</t>
         </is>
       </c>
+      <c r="E512" t="inlineStr"/>
       <c r="F512" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, College of Medicine, Incheon St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26372,6 +26779,7 @@
           <t>Myong JP</t>
         </is>
       </c>
+      <c r="E513" t="inlineStr"/>
       <c r="F513" t="inlineStr">
         <is>
           <t>Department of Occupational and Environmental Medicine, College of Medicine, Seoul St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26404,6 +26812,7 @@
           <t>Lee Y</t>
         </is>
       </c>
+      <c r="E514" t="inlineStr"/>
       <c r="F514" t="inlineStr">
         <is>
           <t>Department of Occupational and Environmental Medicine, College of Medicine, Seoul St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26436,6 +26845,7 @@
           <t>Yim HW</t>
         </is>
       </c>
+      <c r="E515" t="inlineStr"/>
       <c r="F515" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26468,6 +26878,7 @@
           <t>Jeong H</t>
         </is>
       </c>
+      <c r="E516" t="inlineStr"/>
       <c r="F516" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26500,6 +26911,7 @@
           <t>Bae S</t>
         </is>
       </c>
+      <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26532,6 +26944,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -26564,6 +26977,7 @@
           <t>In H</t>
         </is>
       </c>
+      <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -26596,6 +27010,7 @@
           <t>Park A</t>
         </is>
       </c>
+      <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -26628,6 +27043,7 @@
           <t>Jang M</t>
         </is>
       </c>
+      <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -26660,6 +27076,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Busan, Republic of Korea.</t>
@@ -26692,6 +27109,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E523" t="inlineStr"/>
       <c r="F523" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Busan, Republic of Korea.</t>
@@ -26724,6 +27142,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E524" t="inlineStr"/>
       <c r="F524" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Republic of Korea.</t>
@@ -26756,6 +27175,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, College of Medicine, Incheon St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -26788,6 +27208,7 @@
           <t>Ko EM</t>
         </is>
       </c>
+      <c r="E526" t="inlineStr"/>
       <c r="F526" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -26820,6 +27241,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E527" t="inlineStr"/>
       <c r="F527" t="inlineStr">
         <is>
           <t>Division of Infectious Disease Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -26852,6 +27274,7 @@
           <t>Jeong JA</t>
         </is>
       </c>
+      <c r="E528" t="inlineStr"/>
       <c r="F528" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -26884,6 +27307,7 @@
           <t>Lee S</t>
         </is>
       </c>
+      <c r="E529" t="inlineStr"/>
       <c r="F529" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -26916,6 +27340,7 @@
           <t>Kim S</t>
         </is>
       </c>
+      <c r="E530" t="inlineStr"/>
       <c r="F530" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -26948,6 +27373,7 @@
           <t>Ko EM</t>
         </is>
       </c>
+      <c r="E531" t="inlineStr"/>
       <c r="F531" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -26980,6 +27406,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E532" t="inlineStr"/>
       <c r="F532" t="inlineStr">
         <is>
           <t>Division of Infectious Disease Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -27012,6 +27439,7 @@
           <t>Jeong JA</t>
         </is>
       </c>
+      <c r="E533" t="inlineStr"/>
       <c r="F533" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -27044,6 +27472,7 @@
           <t>Lee S</t>
         </is>
       </c>
+      <c r="E534" t="inlineStr"/>
       <c r="F534" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -27076,6 +27505,7 @@
           <t>Kim S</t>
         </is>
       </c>
+      <c r="E535" t="inlineStr"/>
       <c r="F535" t="inlineStr">
         <is>
           <t>Division of Bacterial Disease Research, Center for Infectious Disease Research, National Institute of Infectious Diseases, National Institute of Health, Korea Disease Control and Prevention Agency, Osong, Republic of Korea.</t>
@@ -27108,6 +27538,7 @@
           <t>Jeong YJ</t>
         </is>
       </c>
+      <c r="E536" t="inlineStr"/>
       <c r="F536" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Dongguk University Ilsan Hospital, Goyang, Republic of Korea.</t>
@@ -27140,6 +27571,7 @@
           <t>Kang JY</t>
         </is>
       </c>
+      <c r="E537" t="inlineStr"/>
       <c r="F537" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Cheju Halla General Hospital, Jeju, Republic of Korea.</t>
@@ -27172,6 +27604,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E538" t="inlineStr"/>
       <c r="F538" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27204,6 +27637,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E539" t="inlineStr"/>
       <c r="F539" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27236,6 +27670,7 @@
           <t>Ko Y</t>
         </is>
       </c>
+      <c r="E540" t="inlineStr"/>
       <c r="F540" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Kangdong Sacred Heart Hospital, Hallym University College of Medicine, Seoul, Republic of Korea.</t>
@@ -27268,6 +27703,7 @@
           <t>Oh JY</t>
         </is>
       </c>
+      <c r="E541" t="inlineStr"/>
       <c r="F541" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy, and Critical Care Medicine, Department of Internal Medicine, Korea University Guro Hospital, Korea University College of Medicine, Seoul, Republic of Korea.</t>
@@ -27300,6 +27736,7 @@
           <t>Kang HH</t>
         </is>
       </c>
+      <c r="E542" t="inlineStr"/>
       <c r="F542" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Critical Care and Sleep Medicine, Department of Internal Medicine, Ulsan University Hospital, University of Ulsan College of Medicine, Ulsan, Republic of Korea.</t>
@@ -27332,6 +27769,7 @@
           <t>Lim SC</t>
         </is>
       </c>
+      <c r="E543" t="inlineStr"/>
       <c r="F543" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Chonnam National University Hospital, Gwangju, Republic of Korea.</t>
@@ -27339,7 +27777,7 @@
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Chonnam National University Hospital</t>
+          <t>전남대학교병원</t>
         </is>
       </c>
     </row>
@@ -27364,6 +27802,7 @@
           <t>Hwang HG</t>
         </is>
       </c>
+      <c r="E544" t="inlineStr"/>
       <c r="F544" t="inlineStr">
         <is>
           <t>Department of Medicine, Soonchunhyang University Gumi's Hospital, Gumi, North Kyungsang Province, Republic of Korea.</t>
@@ -27396,6 +27835,7 @@
           <t>Shin KC</t>
         </is>
       </c>
+      <c r="E545" t="inlineStr"/>
       <c r="F545" t="inlineStr">
         <is>
           <t>Division of Pulmonology and Allergy, Department of Internal Medicine, College of Medicine, Yeungnam University and Regional Center for Respiratory Diseases, Yeungnam University Medical Center, Daegu, Republic of Korea.</t>
@@ -27403,7 +27843,7 @@
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Yeungnam University and Regional Center for Respiratory Diseases</t>
+          <t>영남대학교병원</t>
         </is>
       </c>
     </row>
@@ -27428,6 +27868,7 @@
           <t>Lee HB</t>
         </is>
       </c>
+      <c r="E546" t="inlineStr"/>
       <c r="F546" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Research Center for Pulmonary Disorders, Jeonbuk National University Medical School, Jeonju, Republic of Korea.</t>
@@ -27460,6 +27901,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E547" t="inlineStr"/>
       <c r="F547" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27492,6 +27934,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E548" t="inlineStr"/>
       <c r="F548" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Republic of Korea.</t>
@@ -27524,6 +27967,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E549" t="inlineStr"/>
       <c r="F549" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Juhwa-ro 170, Ilsanseo-gu, Goyang, 10380, Republic of Korea.</t>
@@ -27556,6 +28000,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E550" t="inlineStr"/>
       <c r="F550" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Juhwa-ro 170, Ilsanseo-gu, Goyang, 10380, Republic of Korea. gusrud9@yahoo.co.kr.</t>
@@ -27625,6 +28070,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E552" t="inlineStr"/>
       <c r="F552" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27657,6 +28103,7 @@
           <t>Kang JY</t>
         </is>
       </c>
+      <c r="E553" t="inlineStr"/>
       <c r="F553" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Cheju Halla General Hospital, Jeju-do, Republic of Korea.</t>
@@ -27726,6 +28173,7 @@
           <t>Kim JW</t>
         </is>
       </c>
+      <c r="E555" t="inlineStr"/>
       <c r="F555" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Uijeongbu St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27758,6 +28206,7 @@
           <t>Kim YH</t>
         </is>
       </c>
+      <c r="E556" t="inlineStr"/>
       <c r="F556" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Bucheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27790,6 +28239,7 @@
           <t>Yoon HK</t>
         </is>
       </c>
+      <c r="E557" t="inlineStr"/>
       <c r="F557" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Yeouido St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27822,6 +28272,7 @@
           <t>Lee SH</t>
         </is>
       </c>
+      <c r="E558" t="inlineStr"/>
       <c r="F558" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Critical Care and Sleep Medicine, Department of Internal Medicine, Eunpyeong St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -27891,6 +28342,7 @@
           <t>Kim B</t>
         </is>
       </c>
+      <c r="E560" t="inlineStr"/>
       <c r="F560" t="inlineStr">
         <is>
           <t>School of Mathematics and Computing (Mathematics), Yonsei University, Seoul, Republic of Korea.</t>
@@ -27923,6 +28375,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E561" t="inlineStr"/>
       <c r="F561" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea. MDKANG@yuhs.ac. / Institute of Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, Republic of Korea. MDKANG@yuhs.ac.</t>
@@ -27955,6 +28408,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E562" t="inlineStr"/>
       <c r="F562" t="inlineStr">
         <is>
           <t>School of Mathematics and Computing (Mathematics), Yonsei University, Seoul, Republic of Korea. ezhyun@yonsei.ac.kr.</t>
@@ -27987,6 +28441,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E563" t="inlineStr"/>
       <c r="F563" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28019,6 +28474,7 @@
           <t>Park S</t>
         </is>
       </c>
+      <c r="E564" t="inlineStr"/>
       <c r="F564" t="inlineStr">
         <is>
           <t>Institute of Health Services Research, Yonsei University, Seoul, Republic of Korea. / Department of Biostatistics, Graduate School of Public Health, Yonsei University, Seoul, Republic of Korea.</t>
@@ -28051,6 +28507,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E565" t="inlineStr"/>
       <c r="F565" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28083,6 +28540,7 @@
           <t>Sun J</t>
         </is>
       </c>
+      <c r="E566" t="inlineStr"/>
       <c r="F566" t="inlineStr">
         <is>
           <t>Division of Biostatistics, Department of Biomedical Systems Informatics, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -28115,6 +28573,7 @@
           <t>Shin AY</t>
         </is>
       </c>
+      <c r="E567" t="inlineStr"/>
       <c r="F567" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28147,6 +28606,7 @@
           <t>Ha JH</t>
         </is>
       </c>
+      <c r="E568" t="inlineStr"/>
       <c r="F568" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28179,6 +28639,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E569" t="inlineStr"/>
       <c r="F569" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Republic of Korea.</t>
@@ -28211,6 +28672,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E570" t="inlineStr"/>
       <c r="F570" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -28243,6 +28705,7 @@
           <t>Lipman M</t>
         </is>
       </c>
+      <c r="E571" t="inlineStr"/>
       <c r="F571" t="inlineStr">
         <is>
           <t>UCL-TB, University College London, London, UK. / Division of Medicine, UCL Respiratory, University College London, London, UK. / Royal Free London NHS Foundation Trust, London, UK.</t>
@@ -28275,6 +28738,7 @@
           <t>Abubakar I</t>
         </is>
       </c>
+      <c r="E572" t="inlineStr"/>
       <c r="F572" t="inlineStr">
         <is>
           <t>Institute for Global Health, University College London, London, UK.</t>
@@ -28307,6 +28771,7 @@
           <t>Stagg HR</t>
         </is>
       </c>
+      <c r="E573" t="inlineStr"/>
       <c r="F573" t="inlineStr">
         <is>
           <t>Usher Institute, The University of Edinburgh, Edinburgh, UK. helen.stagg@ed.ac.uk.</t>
@@ -28339,6 +28804,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E574" t="inlineStr"/>
       <c r="F574" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea. kimjusang@catholic.ac.kr.</t>
@@ -28371,6 +28837,7 @@
           <t>Ko Y</t>
         </is>
       </c>
+      <c r="E575" t="inlineStr"/>
       <c r="F575" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Kangdong Sacred Heart Hospital, Hallym University College of Medicine, Sung-an ro 150, Kangdonggu, Seoul, 05355, Republic of Korea. koyus@naver.com.</t>
@@ -28403,6 +28870,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E576" t="inlineStr"/>
       <c r="F576" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Daejeon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28435,6 +28903,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E577" t="inlineStr"/>
       <c r="F577" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28467,6 +28936,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E578" t="inlineStr"/>
       <c r="F578" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -28499,6 +28969,7 @@
           <t>Oh JY</t>
         </is>
       </c>
+      <c r="E579" t="inlineStr"/>
       <c r="F579" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy, and Critical Care Medicine, Department of Internal Medicine, Korea University Guro Hospital, Korea University College of Medicine, Seoul, Republic of Korea.</t>
@@ -28531,6 +29002,7 @@
           <t>Jeong YJ</t>
         </is>
       </c>
+      <c r="E580" t="inlineStr"/>
       <c r="F580" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Dongguk University Ilsan Hospital, Goyang, Republic of Korea.</t>
@@ -28563,6 +29035,7 @@
           <t>Kang HH</t>
         </is>
       </c>
+      <c r="E581" t="inlineStr"/>
       <c r="F581" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Critical Care and Sleep Medicine, Department of Internal Medicine, Ulsan University Hospital, Ulsan University College of Medicine, Ulsan, Republic of Korea.</t>
@@ -28595,6 +29068,7 @@
           <t>Kang JY</t>
         </is>
       </c>
+      <c r="E582" t="inlineStr"/>
       <c r="F582" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28627,6 +29101,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E583" t="inlineStr"/>
       <c r="F583" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28659,6 +29134,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E584" t="inlineStr"/>
       <c r="F584" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -28691,6 +29167,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E585" t="inlineStr"/>
       <c r="F585" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, 119 Dandae-ro, Dongnam-gu, Cheonan, 31116, Republic of Korea. jspark@dankook.ac.kr.</t>
@@ -28723,6 +29200,7 @@
           <t>Kwon Y</t>
         </is>
       </c>
+      <c r="E586" t="inlineStr"/>
       <c r="F586" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -28755,6 +29233,7 @@
           <t>Yang J</t>
         </is>
       </c>
+      <c r="E587" t="inlineStr"/>
       <c r="F587" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -28787,6 +29266,7 @@
           <t>Han J</t>
         </is>
       </c>
+      <c r="E588" t="inlineStr"/>
       <c r="F588" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -28819,6 +29299,7 @@
           <t>Jang YJ</t>
         </is>
       </c>
+      <c r="E589" t="inlineStr"/>
       <c r="F589" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -28851,6 +29332,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E590" t="inlineStr"/>
       <c r="F590" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -28883,6 +29365,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E591" t="inlineStr"/>
       <c r="F591" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Daejeon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28915,6 +29398,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E592" t="inlineStr"/>
       <c r="F592" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -28947,6 +29431,7 @@
           <t>Ko Y</t>
         </is>
       </c>
+      <c r="E593" t="inlineStr"/>
       <c r="F593" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Kangdong Sacred Heart Hospital, Hallym University College of Medicine, Seoul, Republic of Korea.</t>
@@ -28979,6 +29464,7 @@
           <t>Oh JY</t>
         </is>
       </c>
+      <c r="E594" t="inlineStr"/>
       <c r="F594" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy, and Critical Care Medicine, Department of Internal Medicine, Korea University Guro Hospital, Korea University College of Medicine, Seoul, Republic of Korea.</t>
@@ -29011,6 +29497,7 @@
           <t>Jeong YJ</t>
         </is>
       </c>
+      <c r="E595" t="inlineStr"/>
       <c r="F595" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Dongguk University Ilsan Hospital, Dongguk University College of Medicine, Goyang, Republic of Korea.</t>
@@ -29043,6 +29530,7 @@
           <t>Kang HH</t>
         </is>
       </c>
+      <c r="E596" t="inlineStr"/>
       <c r="F596" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Critical Care and Sleep Medicine, Department of Internal Medicine, Ulsan University Hospital, University of Ulsan College of Medicine, Ulsan, Republic of Korea.</t>
@@ -29075,6 +29563,7 @@
           <t>Kang JY</t>
         </is>
       </c>
+      <c r="E597" t="inlineStr"/>
       <c r="F597" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, College of Medicine, Seoul St. Mary's Hospital, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -29107,6 +29596,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E598" t="inlineStr"/>
       <c r="F598" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -29139,6 +29629,7 @@
           <t>Seo M</t>
         </is>
       </c>
+      <c r="E599" t="inlineStr"/>
       <c r="F599" t="inlineStr">
         <is>
           <t>Department of Computer Convergence Software, Korea University, Sejong, Republic of Korea.</t>
@@ -29171,6 +29662,7 @@
           <t>Silverman EK</t>
         </is>
       </c>
+      <c r="E600" t="inlineStr"/>
       <c r="F600" t="inlineStr">
         <is>
           <t>Channing Division of Network Medicine, Brigham and Women's Hospital, Boston, MA, USA. / Division of Pulmonary and Critical Care Medicine, Brigham and Women's Hospital, Boston, MA, USA.</t>
@@ -29203,6 +29695,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E601" t="inlineStr"/>
       <c r="F601" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea. kimjusang@catholic.ac.kr. / Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, 56 Dongsu-ro, Bupyeong-gu, Incheon, 21431, Republic of Korea. kimjusang@catholic.ac.kr.</t>
@@ -29235,6 +29728,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E602" t="inlineStr"/>
       <c r="F602" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, 119 Dandae-ro, Dongnam-gu, Cheonan, 31116, Republic of Korea. jspark@dankook.ac.kr.</t>
@@ -29267,6 +29761,7 @@
           <t>Jeong D</t>
         </is>
       </c>
+      <c r="E603" t="inlineStr"/>
       <c r="F603" t="inlineStr">
         <is>
           <t>The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -29299,6 +29794,7 @@
           <t>Kang HY</t>
         </is>
       </c>
+      <c r="E604" t="inlineStr"/>
       <c r="F604" t="inlineStr">
         <is>
           <t>Department of Health Policy and Management, Seoul National University College of Medicine, Seoul, Korea.</t>
@@ -29331,6 +29827,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E605" t="inlineStr"/>
       <c r="F605" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -29363,6 +29860,7 @@
           <t>Lee H</t>
         </is>
       </c>
+      <c r="E606" t="inlineStr"/>
       <c r="F606" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -29395,6 +29893,7 @@
           <t>Yoo BN</t>
         </is>
       </c>
+      <c r="E607" t="inlineStr"/>
       <c r="F607" t="inlineStr">
         <is>
           <t>National Evidence-based Collaborating Agency, Seoul, Korea.</t>
@@ -29427,6 +29926,7 @@
           <t>Kim HS</t>
         </is>
       </c>
+      <c r="E608" t="inlineStr"/>
       <c r="F608" t="inlineStr">
         <is>
           <t>National Evidence-based Collaborating Agency, Seoul, Korea.</t>
@@ -29459,6 +29959,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E609" t="inlineStr"/>
       <c r="F609" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Konyang University College of Medicine, Daejeon, Korea.</t>
@@ -29491,6 +29992,7 @@
           <t>Lee S</t>
         </is>
       </c>
+      <c r="E610" t="inlineStr"/>
       <c r="F610" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, School of Medicine, Kyung Hee University, Seoul, South Korea.</t>
@@ -29523,6 +30025,7 @@
           <t>Kim MJ</t>
         </is>
       </c>
+      <c r="E611" t="inlineStr"/>
       <c r="F611" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, School of Medicine, Kyung Hee University, Seoul, South Korea.</t>
@@ -29555,6 +30058,7 @@
           <t>Lee SH</t>
         </is>
       </c>
+      <c r="E612" t="inlineStr"/>
       <c r="F612" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Sleep and Critical Care Medicine, Department of Internal Medicine, Korea University Ansan Hospital, Ansan-si, South Korea.</t>
@@ -29587,6 +30091,7 @@
           <t>Kim HY</t>
         </is>
       </c>
+      <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr">
         <is>
           <t>Department of Population Health, New York University Grossman School of Medicine, New York, NY, United States.</t>
@@ -29619,6 +30124,7 @@
           <t>Kim HS</t>
         </is>
       </c>
+      <c r="E614" t="inlineStr"/>
       <c r="F614" t="inlineStr">
         <is>
           <t>Department of Health Policy Research, National Evidence-Based Healthcare Collaborating Agency, Seoul, South Korea.</t>
@@ -29651,6 +30157,7 @@
           <t>Oh IH</t>
         </is>
       </c>
+      <c r="E615" t="inlineStr"/>
       <c r="F615" t="inlineStr">
         <is>
           <t>Department of Medicine (AgeTech-Service Convergence Major), School of Medicine, Kyung Hee University, Seoul, South Korea.</t>
@@ -29757,6 +30264,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E618" t="inlineStr"/>
       <c r="F618" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -29900,6 +30408,7 @@
           <t>Jeong YJ</t>
         </is>
       </c>
+      <c r="E622" t="inlineStr"/>
       <c r="F622" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Dongguk University Ilsan Hospital, Goyang, Republic of Korea.</t>
@@ -29932,6 +30441,7 @@
           <t>Kang HH</t>
         </is>
       </c>
+      <c r="E623" t="inlineStr"/>
       <c r="F623" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Critical Care and Sleep Medicine, Department of Internal Medicine, Ulsan University Hospital, University of Ulsan College of Medicine, Ulsan, Republic of Korea.</t>
@@ -29964,6 +30474,7 @@
           <t>Kang JY</t>
         </is>
       </c>
+      <c r="E624" t="inlineStr"/>
       <c r="F624" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -29996,6 +30507,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E625" t="inlineStr"/>
       <c r="F625" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -30028,6 +30540,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Republic of Korea.</t>
@@ -30060,6 +30573,7 @@
           <t>Kwon Y</t>
         </is>
       </c>
+      <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -30092,6 +30606,7 @@
           <t>Yang J</t>
         </is>
       </c>
+      <c r="E628" t="inlineStr"/>
       <c r="F628" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -30124,6 +30639,7 @@
           <t>Han J</t>
         </is>
       </c>
+      <c r="E629" t="inlineStr"/>
       <c r="F629" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -30156,6 +30672,7 @@
           <t>Jang YJ</t>
         </is>
       </c>
+      <c r="E630" t="inlineStr"/>
       <c r="F630" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Korea Disease Control and Prevention Agency, Cheongju, Republic of Korea.</t>
@@ -30188,6 +30705,7 @@
           <t>Lee MK</t>
         </is>
       </c>
+      <c r="E631" t="inlineStr"/>
       <c r="F631" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Hospital, Pusan National University School of Medicine, Pusan, Republic of Korea.</t>
@@ -30220,6 +30738,7 @@
           <t>Jegal Y</t>
         </is>
       </c>
+      <c r="E632" t="inlineStr"/>
       <c r="F632" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Critical Care and Sleep Medicine, Department of Internal Medicine, Ulsan University Hospital, Ulsan University College of Medicine, Ulsan, Republic of Korea.</t>
@@ -30252,6 +30771,7 @@
           <t>Kim YC</t>
         </is>
       </c>
+      <c r="E633" t="inlineStr"/>
       <c r="F633" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Chonnam National University Hwasun Hospital, Chonnam National University Medical School, Hwasun, Republic of Korea.</t>
@@ -30259,7 +30779,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Chonnam National University Hwasun Hospital</t>
+          <t>화순전남대학교병원</t>
         </is>
       </c>
     </row>
@@ -30321,6 +30841,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E635" t="inlineStr"/>
       <c r="F635" t="inlineStr">
         <is>
           <t>School of Environment, Yale University, New Haven, CT, USA.</t>
@@ -30353,6 +30874,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E636" t="inlineStr"/>
       <c r="F636" t="inlineStr">
         <is>
           <t>Division of Pulmonology and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, Seoul, Republic of Korea.</t>
@@ -30385,6 +30907,7 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E637" t="inlineStr"/>
       <c r="F637" t="inlineStr">
         <is>
           <t>Korean National Tuberculosis Association, Seoul, Republic of Korea.</t>
@@ -31046,6 +31569,7 @@
           <t>Lee EH</t>
         </is>
       </c>
+      <c r="E655" t="inlineStr"/>
       <c r="F655" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea. / Center for Digital Health, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31078,6 +31602,7 @@
           <t>Son NH</t>
         </is>
       </c>
+      <c r="E656" t="inlineStr"/>
       <c r="F656" t="inlineStr">
         <is>
           <t>Center for Digital Health, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea. / Data Science Team (Biostatistician), Center for Digital Health, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31110,6 +31635,7 @@
           <t>Kwak SH</t>
         </is>
       </c>
+      <c r="E657" t="inlineStr"/>
       <c r="F657" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31142,6 +31668,7 @@
           <t>Choi JS</t>
         </is>
       </c>
+      <c r="E658" t="inlineStr"/>
       <c r="F658" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31174,6 +31701,7 @@
           <t>Kim MC</t>
         </is>
       </c>
+      <c r="E659" t="inlineStr"/>
       <c r="F659" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31206,6 +31734,7 @@
           <t>Seol CH</t>
         </is>
       </c>
+      <c r="E660" t="inlineStr"/>
       <c r="F660" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31238,6 +31767,7 @@
           <t>Kim SR</t>
         </is>
       </c>
+      <c r="E661" t="inlineStr"/>
       <c r="F661" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea. / Center for Digital Health, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31270,6 +31800,7 @@
           <t>Park BH</t>
         </is>
       </c>
+      <c r="E662" t="inlineStr"/>
       <c r="F662" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Allergy and Critical Care Medicine, Department of Internal Medicine, Yongin Severance Hospital, Yonsei University College of Medicine, Yongin, Gyeonggi-do, Republic of Korea.</t>
@@ -31302,6 +31833,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E663" t="inlineStr"/>
       <c r="F663" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Severance Hospital, Yonsei University College of Medicine, 50-1 Yonsei-ro, Seodaemun-gu, Seoul, 03722, Republic of Korea. MDKANG@yuhs.ac. / Institute of Immunology and Immunological Diseases, Yonsei University College of Medicine, 50-1 Yonsei-ro, Seodaemun-gu, Seoul, 03722, Republic of Korea. MDKANG@yuhs.ac.</t>
@@ -31334,6 +31866,7 @@
           <t>Yang J</t>
         </is>
       </c>
+      <c r="E664" t="inlineStr"/>
       <c r="F664" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31366,6 +31899,7 @@
           <t>Kwon Y</t>
         </is>
       </c>
+      <c r="E665" t="inlineStr"/>
       <c r="F665" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31398,6 +31932,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E666" t="inlineStr"/>
       <c r="F666" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31430,6 +31965,7 @@
           <t>Jang Y</t>
         </is>
       </c>
+      <c r="E667" t="inlineStr"/>
       <c r="F667" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31462,6 +31998,7 @@
           <t>Han J</t>
         </is>
       </c>
+      <c r="E668" t="inlineStr"/>
       <c r="F668" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31494,6 +32031,7 @@
           <t>Kim D</t>
         </is>
       </c>
+      <c r="E669" t="inlineStr"/>
       <c r="F669" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31526,6 +32064,7 @@
           <t>Jeong H</t>
         </is>
       </c>
+      <c r="E670" t="inlineStr"/>
       <c r="F670" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31558,6 +32097,7 @@
           <t>Park H</t>
         </is>
       </c>
+      <c r="E671" t="inlineStr"/>
       <c r="F671" t="inlineStr">
         <is>
           <t>Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31590,6 +32130,7 @@
           <t>Shim E</t>
         </is>
       </c>
+      <c r="E672" t="inlineStr"/>
       <c r="F672" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Prevention and Control, Bureau of Infectious Disease Policy, Korea Disease Control and Prevention Agency, Cheongju, Korea.</t>
@@ -31622,6 +32163,7 @@
           <t>Cho H</t>
         </is>
       </c>
+      <c r="E673" t="inlineStr"/>
       <c r="F673" t="inlineStr">
         <is>
           <t>School of Mathematics and Computing, Yonsei University, Seodaemun-gu, South Korea.</t>
@@ -31654,6 +32196,7 @@
           <t>Park Y</t>
         </is>
       </c>
+      <c r="E674" t="inlineStr"/>
       <c r="F674" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Yonsei University College of Medicine, Seodaemun-gu, South Korea.</t>
@@ -31686,6 +32229,7 @@
           <t>Seok J</t>
         </is>
       </c>
+      <c r="E675" t="inlineStr"/>
       <c r="F675" t="inlineStr">
         <is>
           <t>School of Mathematics and Computing, Yonsei University, Seodaemun-gu, South Korea.</t>
@@ -31755,6 +32299,7 @@
           <t>Choi JY</t>
         </is>
       </c>
+      <c r="E677" t="inlineStr"/>
       <c r="F677" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Yonsei University College of Medicine, Seodaemun-gu, South Korea.</t>
@@ -31787,6 +32332,7 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E678" t="inlineStr"/>
       <c r="F678" t="inlineStr">
         <is>
           <t>Korean National Tuberculosis Association, Seoul, South Korea.</t>
@@ -31819,6 +32365,7 @@
           <t>Kang YA</t>
         </is>
       </c>
+      <c r="E679" t="inlineStr"/>
       <c r="F679" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Yonsei University College of Medicine, Seodaemun-gu, South Korea ezhyun@yonsei.ac.kr MDKANG@yuhs.ac. / Institute of Immunology and Immunological Disease, Yonsei University College of Medicine, Seoul, South Korea.</t>
@@ -31851,6 +32398,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E680" t="inlineStr"/>
       <c r="F680" t="inlineStr">
         <is>
           <t>School of Mathematics and Computing, Yonsei University, Seodaemun-gu, South Korea ezhyun@yonsei.ac.kr MDKANG@yuhs.ac.</t>
@@ -32549,6 +33097,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E699" t="inlineStr"/>
       <c r="F699" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, College of Medicine, Pusan National University, South Korea. / Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, Busan, South Korea.</t>
@@ -32581,6 +33130,7 @@
           <t>Lee M</t>
         </is>
       </c>
+      <c r="E700" t="inlineStr"/>
       <c r="F700" t="inlineStr">
         <is>
           <t>Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, Busan, South Korea.</t>
@@ -32613,6 +33163,7 @@
           <t>Park W</t>
         </is>
       </c>
+      <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr">
         <is>
           <t>Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, Busan, South Korea.</t>
@@ -32645,6 +33196,7 @@
           <t>Kim S</t>
         </is>
       </c>
+      <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr">
         <is>
           <t>Korea Disease Control and Prevention Agency, Cheongju, South Korea.</t>
@@ -32677,6 +33229,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr">
         <is>
           <t>Korea Disease Control and Prevention Agency, Cheongju, South Korea.</t>
@@ -32709,6 +33262,7 @@
           <t>Choi BY</t>
         </is>
       </c>
+      <c r="E704" t="inlineStr"/>
       <c r="F704" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine/Institute of Community Health, College of Medicine, Hanyang University, Seoul, South Korea.</t>
@@ -32741,6 +33295,7 @@
           <t>Kim C</t>
         </is>
       </c>
+      <c r="E705" t="inlineStr"/>
       <c r="F705" t="inlineStr">
         <is>
           <t>Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, Busan, South Korea. / Department of Preventive Medicine, College of Medicine, Pusan National University, Busan, South Korea.</t>
@@ -33254,6 +33809,9 @@
           <t>Kwak N</t>
         </is>
       </c>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -33276,6 +33834,9 @@
           <t>Hwang SS</t>
         </is>
       </c>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -33298,6 +33859,9 @@
           <t>Yim JJ</t>
         </is>
       </c>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -33320,6 +33884,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E722" t="inlineStr"/>
       <c r="F722" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Daejeon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Korea.</t>
@@ -33352,6 +33917,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E723" t="inlineStr"/>
       <c r="F723" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Korea.</t>
@@ -33384,6 +33950,7 @@
           <t>Ko Y</t>
         </is>
       </c>
+      <c r="E724" t="inlineStr"/>
       <c r="F724" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy and Critical Care Medicine, Department of Internal Medicine, Kangdong Sacred Heart Hospital, Hallym University College of Medicine, Seoul, Korea.</t>
@@ -33416,6 +33983,7 @@
           <t>Oh JY</t>
         </is>
       </c>
+      <c r="E725" t="inlineStr"/>
       <c r="F725" t="inlineStr">
         <is>
           <t>Division of Pulmonary, Allergy, and Critical Care Medicine, Department of Internal Medicine, Korea University Guro Hospital, Korea University College of Medicine, Seoul, Korea.</t>
@@ -33448,6 +34016,7 @@
           <t>Kang JY</t>
         </is>
       </c>
+      <c r="E726" t="inlineStr"/>
       <c r="F726" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Korea.</t>
@@ -33480,6 +34049,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E727" t="inlineStr"/>
       <c r="F727" t="inlineStr">
         <is>
           <t>Division of TB Epidemic Investigation, Korea Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -33512,6 +34082,7 @@
           <t>Park YJ</t>
         </is>
       </c>
+      <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr">
         <is>
           <t>Division of TB Epidemic Investigation, Korea Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -33544,6 +34115,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E729" t="inlineStr"/>
       <c r="F729" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Inje University Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Korea.</t>
@@ -33576,6 +34148,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E730" t="inlineStr"/>
       <c r="F730" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Korea.</t>
@@ -33608,6 +34181,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Korea.</t>
@@ -33640,6 +34214,7 @@
           <t>Kim H</t>
         </is>
       </c>
+      <c r="E732" t="inlineStr"/>
       <c r="F732" t="inlineStr">
         <is>
           <t>BK21Plus Program in Embodiment: Health-Society Interaction, Department of Public Health Sciences, Graduate School, Korea University, Seoul, Korea. / School of Forestry and Environmental Studies, Yale University, New Haven, CT, USA.</t>
@@ -33672,6 +34247,7 @@
           <t>Yu S</t>
         </is>
       </c>
+      <c r="E733" t="inlineStr"/>
       <c r="F733" t="inlineStr">
         <is>
           <t>BK21Plus Program in Embodiment: Health-Society Interaction, Department of Public Health Sciences, Graduate School, Korea University, Seoul, Korea. / Research Center, the Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Seoul, Korea. / School of Health Policy and Management, Korea University College of Health Science, Seoul, Korea.</t>
@@ -33704,6 +34280,7 @@
           <t>Choi H</t>
         </is>
       </c>
+      <c r="E734" t="inlineStr"/>
       <c r="F734" t="inlineStr">
         <is>
           <t>Research Center, the Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Seoul, Korea. / Department of Preventive Medicine, Konyang University College of Medicine, Daejeon, Korea.</t>
@@ -33736,6 +34313,7 @@
           <t>Jeon D</t>
         </is>
       </c>
+      <c r="E735" t="inlineStr"/>
       <c r="F735" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, Pusan National University Yangsan Hospital, Yangsan, Korea.</t>
@@ -33805,6 +34383,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E737" t="inlineStr"/>
       <c r="F737" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -33911,6 +34490,7 @@
           <t>Rangaka MX</t>
         </is>
       </c>
+      <c r="E740" t="inlineStr"/>
       <c r="F740" t="inlineStr">
         <is>
           <t>Institute for Global Health, University College London, London, London, United Kingdom.</t>
@@ -33943,6 +34523,7 @@
           <t>Myong JP</t>
         </is>
       </c>
+      <c r="E741" t="inlineStr"/>
       <c r="F741" t="inlineStr">
         <is>
           <t>Department of Occupational and Environmental Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Korea (the Republic of).</t>
@@ -34012,6 +34593,7 @@
           <t>Lim JU</t>
         </is>
       </c>
+      <c r="E743" t="inlineStr"/>
       <c r="F743" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Korea (the Republic of).</t>
@@ -34044,6 +34626,7 @@
           <t>Lee Y</t>
         </is>
       </c>
+      <c r="E744" t="inlineStr"/>
       <c r="F744" t="inlineStr">
         <is>
           <t>Department of Occupational and Environmental Medicine, Seoul St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Korea (the Republic of).</t>
@@ -34076,6 +34659,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E745" t="inlineStr"/>
       <c r="F745" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Korea (the Republic of).</t>
@@ -34108,6 +34692,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Korea (the Republic of).</t>
@@ -34140,6 +34725,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, Cheonan, Chungcheongnam-do, Korea (the Republic of).</t>
@@ -34172,6 +34758,7 @@
           <t>Cho KS</t>
         </is>
       </c>
+      <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr">
         <is>
           <t>Division of Social Service Projects, Office for Social Welfare Policy, Korea Ministry of Health and Welfare, Sejong, Sejong, Korea (the Republic of).</t>
@@ -34204,6 +34791,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E749" t="inlineStr"/>
       <c r="F749" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea kimjusang@catholic.ac.kr.</t>
@@ -34236,6 +34824,7 @@
           <t>Park SY</t>
         </is>
       </c>
+      <c r="E750" t="inlineStr"/>
       <c r="F750" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -34268,6 +34857,7 @@
           <t>Han S</t>
         </is>
       </c>
+      <c r="E751" t="inlineStr"/>
       <c r="F751" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -34300,6 +34890,7 @@
           <t>Kim YM</t>
         </is>
       </c>
+      <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -34332,6 +34923,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E753" t="inlineStr"/>
       <c r="F753" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -34364,6 +34956,7 @@
           <t>Lee S</t>
         </is>
       </c>
+      <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -34396,6 +34989,7 @@
           <t>Yang J</t>
         </is>
       </c>
+      <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -34428,6 +35022,7 @@
           <t>Kim UN</t>
         </is>
       </c>
+      <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea. unnakim@korea.kr.</t>
@@ -34460,6 +35055,7 @@
           <t>Park MS</t>
         </is>
       </c>
+      <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
           <t>Division of TB Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea. pmsun4686@naver.com.</t>
@@ -34492,6 +35088,7 @@
           <t>Yang J</t>
         </is>
       </c>
+      <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr">
         <is>
           <t>Korea Centers for Disease Control &amp; Prevention, Cheongju, Republic of Korea.</t>
@@ -34524,6 +35121,7 @@
           <t>Lee S</t>
         </is>
       </c>
+      <c r="E759" t="inlineStr"/>
       <c r="F759" t="inlineStr">
         <is>
           <t>Korea Centers for Disease Control &amp; Prevention, Cheongju, Republic of Korea.</t>
@@ -34556,6 +35154,7 @@
           <t>Oh S</t>
         </is>
       </c>
+      <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
           <t>Korea Centers for Disease Control &amp; Prevention, Cheongju, Republic of Korea.</t>
@@ -34588,6 +35187,7 @@
           <t>Han S</t>
         </is>
       </c>
+      <c r="E761" t="inlineStr"/>
       <c r="F761" t="inlineStr">
         <is>
           <t>Korea Centers for Disease Control &amp; Prevention, Cheongju, Republic of Korea.</t>
@@ -34620,6 +35220,7 @@
           <t>Park SY</t>
         </is>
       </c>
+      <c r="E762" t="inlineStr"/>
       <c r="F762" t="inlineStr">
         <is>
           <t>Korea Centers for Disease Control &amp; Prevention, Cheongju, Republic of Korea.</t>
@@ -34652,6 +35253,7 @@
           <t>Kim Y</t>
         </is>
       </c>
+      <c r="E763" t="inlineStr"/>
       <c r="F763" t="inlineStr">
         <is>
           <t>Korea Centers for Disease Control &amp; Prevention, Cheongju, Republic of Korea.</t>
@@ -34684,6 +35286,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E764" t="inlineStr"/>
       <c r="F764" t="inlineStr">
         <is>
           <t>Korea Centers for Disease Control &amp; Prevention, Cheongju, Republic of Korea.</t>
@@ -34753,6 +35356,7 @@
           <t>Lee M</t>
         </is>
       </c>
+      <c r="E766" t="inlineStr"/>
       <c r="F766" t="inlineStr">
         <is>
           <t>International Tuberculosis Research Center, Seoul.</t>
@@ -34785,6 +35389,7 @@
           <t>Han J</t>
         </is>
       </c>
+      <c r="E767" t="inlineStr"/>
       <c r="F767" t="inlineStr">
         <is>
           <t>Medical Research Collaborating Center, Seoul National University Hospital, Seoul.</t>
@@ -34817,6 +35422,7 @@
           <t>Kim YR</t>
         </is>
       </c>
+      <c r="E768" t="inlineStr"/>
       <c r="F768" t="inlineStr">
         <is>
           <t>International Tuberculosis Research Center, Seoul.</t>
@@ -34849,6 +35455,7 @@
           <t>Kwak N</t>
         </is>
       </c>
+      <c r="E769" t="inlineStr"/>
       <c r="F769" t="inlineStr">
         <is>
           <t>Medical Squadron, Operation Command, Republic of Korea Air Force, Osan.</t>
@@ -34881,6 +35488,7 @@
           <t>Kim JH</t>
         </is>
       </c>
+      <c r="E770" t="inlineStr"/>
       <c r="F770" t="inlineStr">
         <is>
           <t>Gijang Public Health Center, Busan.</t>
@@ -34913,6 +35521,7 @@
           <t>Park O</t>
         </is>
       </c>
+      <c r="E771" t="inlineStr"/>
       <c r="F771" t="inlineStr">
         <is>
           <t>Division of Risk Assessment and International Cooperation, Korea Centers for Disease Control and Prevention, Cheongju.</t>
@@ -34945,6 +35554,7 @@
           <t>Shin S</t>
         </is>
       </c>
+      <c r="E772" t="inlineStr"/>
       <c r="F772" t="inlineStr">
         <is>
           <t>Korean Institute of Tuberculosis, Cheongju.</t>
@@ -34977,6 +35587,7 @@
           <t>Moon HS</t>
         </is>
       </c>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="inlineStr">
         <is>
           <t>Division of Pulmonology, Department of Internal Medicine, St Paul's Hospital, The Catholic University of Korea College of Medicine, Seoul.</t>
@@ -35009,6 +35620,7 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E774" t="inlineStr"/>
       <c r="F774" t="inlineStr">
         <is>
           <t>Korean Institute of Tuberculosis, Cheongju.</t>
@@ -35041,6 +35653,7 @@
           <t>Jang MJ</t>
         </is>
       </c>
+      <c r="E775" t="inlineStr"/>
       <c r="F775" t="inlineStr">
         <is>
           <t>Medical Research Collaborating Center, Seoul National University Hospital, Seoul.</t>
@@ -35073,6 +35686,7 @@
           <t>Yim JJ</t>
         </is>
       </c>
+      <c r="E776" t="inlineStr"/>
       <c r="F776" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Seoul National University College of Medicine, Seoul, South Korea.</t>
@@ -35105,6 +35719,7 @@
           <t>Min J</t>
         </is>
       </c>
+      <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Daejeon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -35137,6 +35752,7 @@
           <t>Kim JS</t>
         </is>
       </c>
+      <c r="E778" t="inlineStr"/>
       <c r="F778" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -35169,6 +35785,7 @@
           <t>Kim HW</t>
         </is>
       </c>
+      <c r="E779" t="inlineStr"/>
       <c r="F779" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -35201,6 +35818,7 @@
           <t>Shin AY</t>
         </is>
       </c>
+      <c r="E780" t="inlineStr"/>
       <c r="F780" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Incheon St. Mary's Hospital, College of Medicine, The Catholic University of Korea, Seoul, Republic of Korea.</t>
@@ -35233,6 +35851,7 @@
           <t>Koo HK</t>
         </is>
       </c>
+      <c r="E781" t="inlineStr"/>
       <c r="F781" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -35265,6 +35884,7 @@
           <t>Lee SS</t>
         </is>
       </c>
+      <c r="E782" t="inlineStr"/>
       <c r="F782" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Ilsan Paik Hospital, Inje University College of Medicine, Goyang, Republic of Korea.</t>
@@ -35297,6 +35917,7 @@
           <t>Kim YK</t>
         </is>
       </c>
+      <c r="E783" t="inlineStr"/>
       <c r="F783" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Allergy Medicine, Department of Internal Medicine, Soonchunhyang University College of Medicine, Seoul, Republic of Korea.</t>
@@ -35329,6 +35950,7 @@
           <t>Shin KC</t>
         </is>
       </c>
+      <c r="E784" t="inlineStr"/>
       <c r="F784" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, Yeungnam University Medical Center, College of Medicine, Yeungnam University, Daegu, Republic of Korea.</t>
@@ -35336,7 +35958,7 @@
       </c>
       <c r="G784" t="inlineStr">
         <is>
-          <t>Yeungnam University Medical Center</t>
+          <t>영남대학교병원</t>
         </is>
       </c>
     </row>
@@ -35361,6 +35983,7 @@
           <t>Chang JH</t>
         </is>
       </c>
+      <c r="E785" t="inlineStr"/>
       <c r="F785" t="inlineStr">
         <is>
           <t>Division of Pulmonary and Critical Care Medicine, Department of Internal Medicine, College of Medicine, Ewha Womans University, Seoul, Republic of Korea.</t>
@@ -35393,6 +36016,7 @@
           <t>Chun G</t>
         </is>
       </c>
+      <c r="E786" t="inlineStr"/>
       <c r="F786" t="inlineStr">
         <is>
           <t>Division of TB Epidemic Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -35425,6 +36049,7 @@
           <t>Lee J</t>
         </is>
       </c>
+      <c r="E787" t="inlineStr"/>
       <c r="F787" t="inlineStr">
         <is>
           <t>Division of TB Epidemic Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -35457,6 +36082,7 @@
           <t>Park MS</t>
         </is>
       </c>
+      <c r="E788" t="inlineStr"/>
       <c r="F788" t="inlineStr">
         <is>
           <t>Division of TB Epidemic Investigation, Korea Centers for Disease Control and Prevention, Osong, Republic of Korea.</t>
@@ -35489,6 +36115,7 @@
           <t>Park JS</t>
         </is>
       </c>
+      <c r="E789" t="inlineStr"/>
       <c r="F789" t="inlineStr">
         <is>
           <t>Division of Pulmonary Medicine, Department of Internal Medicine, Dankook University College of Medicine, 119 Dandae-ro, Dongnam-gu, Cheonan, 31116, Republic of Korea. jspark@dankook.ac.kr.</t>
@@ -35558,6 +36185,7 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E791" t="inlineStr"/>
       <c r="F791" t="inlineStr">
         <is>
           <t>The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -35590,6 +36218,7 @@
           <t>Oh KH</t>
         </is>
       </c>
+      <c r="E792" t="inlineStr"/>
       <c r="F792" t="inlineStr">
         <is>
           <t>Department of Program Cooperation, The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -35622,6 +36251,7 @@
           <t>Oh HW</t>
         </is>
       </c>
+      <c r="E793" t="inlineStr"/>
       <c r="F793" t="inlineStr">
         <is>
           <t>Gwangju Jeonnam Branch, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -35691,6 +36321,7 @@
           <t>Kim DS</t>
         </is>
       </c>
+      <c r="E795" t="inlineStr"/>
       <c r="F795" t="inlineStr">
         <is>
           <t>Jeju Center for Infection Control, Jeju, Korea.</t>
@@ -35723,6 +36354,7 @@
           <t>Bae JM</t>
         </is>
       </c>
+      <c r="E796" t="inlineStr"/>
       <c r="F796" t="inlineStr">
         <is>
           <t>Jeju Center for Infection Control, Jeju, Korea. / Department of Preventive Medicine, Jeju National University School of Medicine, Jeju, Korea.</t>
@@ -35755,6 +36387,7 @@
           <t>Mok J</t>
         </is>
       </c>
+      <c r="E797" t="inlineStr"/>
       <c r="F797" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, College of Medicine, Pusan National University, Busan, South Korea. / Medical Research Institute, Pusan National University Hospital, Busan, South Korea. / Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, 179 Gudeok-ro, Seo-gu, Busan, 49241, South Korea.</t>
@@ -35787,6 +36420,7 @@
           <t>An D</t>
         </is>
       </c>
+      <c r="E798" t="inlineStr"/>
       <c r="F798" t="inlineStr">
         <is>
           <t>Department of Statistics, Pukyong National University, Busan, South Korea.</t>
@@ -35819,6 +36453,7 @@
           <t>Kim S</t>
         </is>
       </c>
+      <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
           <t>Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, 179 Gudeok-ro, Seo-gu, Busan, 49241, South Korea.</t>
@@ -35851,6 +36486,7 @@
           <t>Lee M</t>
         </is>
       </c>
+      <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
           <t>Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, 179 Gudeok-ro, Seo-gu, Busan, 49241, South Korea.</t>
@@ -35883,6 +36519,7 @@
           <t>Kim C</t>
         </is>
       </c>
+      <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
           <t>Medical Research Institute, Pusan National University Hospital, Busan, South Korea. / Busan Center for Infectious Disease Control and Prevention, Pusan National University Hospital, 179 Gudeok-ro, Seo-gu, Busan, 49241, South Korea. / Department of Preventive Medicine, College of Medicine, Pusan National University, Busan, South Korea.</t>
@@ -35952,6 +36589,7 @@
           <t>Kim EH</t>
         </is>
       </c>
+      <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Jeju National University School of Medicine, Jeju, Korea.</t>
@@ -35984,6 +36622,7 @@
           <t>Bae JM</t>
         </is>
       </c>
+      <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
           <t>Department of Preventive Medicine, Jeju National University School of Medicine, Jeju, Korea.</t>
@@ -36016,6 +36655,7 @@
           <t>Lee Y</t>
         </is>
       </c>
+      <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
           <t>Graduate School of Public Health, Yonsei University Health System, Room 410, Administration B/D, 50-1 Yonsei-Ro, Seodaemun-Gu, Seoul, 120-752, Republic of Korea. leeyuri23@yuhs.ac.</t>
@@ -36048,6 +36688,7 @@
           <t>Han MA</t>
         </is>
       </c>
+      <c r="E806" t="inlineStr"/>
       <c r="F806" t="inlineStr">
         <is>
           <t>1 College of Medicine, Chosun University, Gwangju, Republic of Korea.</t>
@@ -36080,6 +36721,7 @@
           <t>Kang HY</t>
         </is>
       </c>
+      <c r="E807" t="inlineStr"/>
       <c r="F807" t="inlineStr">
         <is>
           <t>Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36112,6 +36754,7 @@
           <t>Yoo H</t>
         </is>
       </c>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="inlineStr">
         <is>
           <t>Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36144,6 +36787,7 @@
           <t>Park W</t>
         </is>
       </c>
+      <c r="E809" t="inlineStr"/>
       <c r="F809" t="inlineStr">
         <is>
           <t>Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36176,6 +36820,7 @@
           <t>Go U</t>
         </is>
       </c>
+      <c r="E810" t="inlineStr"/>
       <c r="F810" t="inlineStr">
         <is>
           <t>Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36208,6 +36853,7 @@
           <t>Jeong E</t>
         </is>
       </c>
+      <c r="E811" t="inlineStr"/>
       <c r="F811" t="inlineStr">
         <is>
           <t>Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36240,6 +36886,7 @@
           <t>Jung KS</t>
         </is>
       </c>
+      <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr">
         <is>
           <t>Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36272,6 +36919,7 @@
           <t>Son H</t>
         </is>
       </c>
+      <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr">
         <is>
           <t>Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36304,6 +36952,7 @@
           <t>Onozaki I</t>
         </is>
       </c>
+      <c r="E814" t="inlineStr"/>
       <c r="F814" t="inlineStr">
         <is>
           <t>World Health Organization, Geneva, Switzerland.</t>
@@ -36336,6 +36985,7 @@
           <t>Law I</t>
         </is>
       </c>
+      <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr">
         <is>
           <t>World Health Organization, Geneva, Switzerland.</t>
@@ -36368,6 +37018,7 @@
           <t>Sismanidis C</t>
         </is>
       </c>
+      <c r="E816" t="inlineStr"/>
       <c r="F816" t="inlineStr">
         <is>
           <t>World Health Organization, Geneva, Switzerland.</t>
@@ -36400,6 +37051,7 @@
           <t>Zignol M</t>
         </is>
       </c>
+      <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr">
         <is>
           <t>World Health Organization, Geneva, Switzerland.</t>
@@ -36432,6 +37084,7 @@
           <t>Glaziou P</t>
         </is>
       </c>
+      <c r="E818" t="inlineStr"/>
       <c r="F818" t="inlineStr">
         <is>
           <t>World Health Organization, Geneva, Switzerland.</t>
@@ -36464,6 +37117,7 @@
           <t>Floyd K</t>
         </is>
       </c>
+      <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr">
         <is>
           <t>World Health Organization, Geneva, Switzerland.</t>
@@ -36496,6 +37150,7 @@
           <t>Lee H</t>
         </is>
       </c>
+      <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr">
         <is>
           <t>Division of Epidemic Intelligence Service, Korea Centers for Disease Control and Prevention, Cheongju, Korea.</t>
@@ -36528,6 +37183,7 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E821" t="inlineStr"/>
       <c r="F821" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, College of Medicine, Catholic University of Korea, Seoul, Korea.</t>
@@ -36560,6 +37216,7 @@
           <t>Ryoo S</t>
         </is>
       </c>
+      <c r="E822" t="inlineStr"/>
       <c r="F822" t="inlineStr">
         <is>
           <t>The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -36592,6 +37249,7 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E823" t="inlineStr"/>
       <c r="F823" t="inlineStr">
         <is>
           <t>The Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Cheongju, Korea.</t>
@@ -36624,6 +37282,7 @@
           <t>Kang BJ</t>
         </is>
       </c>
+      <c r="E824" t="inlineStr"/>
       <c r="F824" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36656,6 +37315,7 @@
           <t>Jo KW</t>
         </is>
       </c>
+      <c r="E825" t="inlineStr"/>
       <c r="F825" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36688,6 +37348,7 @@
           <t>Park TS</t>
         </is>
       </c>
+      <c r="E826" t="inlineStr"/>
       <c r="F826" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36720,6 +37381,7 @@
           <t>Yoo JW</t>
         </is>
       </c>
+      <c r="E827" t="inlineStr"/>
       <c r="F827" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36752,6 +37414,7 @@
           <t>Lee SW</t>
         </is>
       </c>
+      <c r="E828" t="inlineStr"/>
       <c r="F828" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36784,6 +37447,7 @@
           <t>Choi CM</t>
         </is>
       </c>
+      <c r="E829" t="inlineStr"/>
       <c r="F829" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36816,6 +37480,7 @@
           <t>Oh YM</t>
         </is>
       </c>
+      <c r="E830" t="inlineStr"/>
       <c r="F830" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36848,6 +37513,7 @@
           <t>Lee SD</t>
         </is>
       </c>
+      <c r="E831" t="inlineStr"/>
       <c r="F831" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36880,6 +37546,7 @@
           <t>Kim WS</t>
         </is>
       </c>
+      <c r="E832" t="inlineStr"/>
       <c r="F832" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36912,6 +37579,7 @@
           <t>Kim DS</t>
         </is>
       </c>
+      <c r="E833" t="inlineStr"/>
       <c r="F833" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36944,6 +37612,7 @@
           <t>Shim TS</t>
         </is>
       </c>
+      <c r="E834" t="inlineStr"/>
       <c r="F834" t="inlineStr">
         <is>
           <t>Department of Pulmonary and Critical Care Medicine, University of Ulsan College of Medicine, Asan Medical Center, Seoul, Korea.</t>
@@ -36976,6 +37645,7 @@
           <t>Falzon D</t>
         </is>
       </c>
+      <c r="E835" t="inlineStr"/>
       <c r="F835" t="inlineStr">
         <is>
           <t>Stop TB Department, World Health Organization, Geneva, Switzerland. falzond@who.int</t>
@@ -37008,6 +37678,9 @@
           <t>Jaramillo E</t>
         </is>
       </c>
+      <c r="E836" t="inlineStr"/>
+      <c r="F836" t="inlineStr"/>
+      <c r="G836" t="inlineStr"/>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -37030,6 +37703,9 @@
           <t>Wares F</t>
         </is>
       </c>
+      <c r="E837" t="inlineStr"/>
+      <c r="F837" t="inlineStr"/>
+      <c r="G837" t="inlineStr"/>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -37052,6 +37728,9 @@
           <t>Zignol M</t>
         </is>
       </c>
+      <c r="E838" t="inlineStr"/>
+      <c r="F838" t="inlineStr"/>
+      <c r="G838" t="inlineStr"/>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -37074,6 +37753,9 @@
           <t>Floyd K</t>
         </is>
       </c>
+      <c r="E839" t="inlineStr"/>
+      <c r="F839" t="inlineStr"/>
+      <c r="G839" t="inlineStr"/>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -37096,6 +37778,9 @@
           <t>Raviglione MC</t>
         </is>
       </c>
+      <c r="E840" t="inlineStr"/>
+      <c r="F840" t="inlineStr"/>
+      <c r="G840" t="inlineStr"/>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -37118,6 +37803,7 @@
           <t>Park YK</t>
         </is>
       </c>
+      <c r="E841" t="inlineStr"/>
       <c r="F841" t="inlineStr">
         <is>
           <t>Korean Institute of Tuberculosis, Cheongwon, Korea.</t>
@@ -37150,6 +37836,9 @@
           <t>Park YS</t>
         </is>
       </c>
+      <c r="E842" t="inlineStr"/>
+      <c r="F842" t="inlineStr"/>
+      <c r="G842" t="inlineStr"/>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -37172,6 +37861,9 @@
           <t>Na KI</t>
         </is>
       </c>
+      <c r="E843" t="inlineStr"/>
+      <c r="F843" t="inlineStr"/>
+      <c r="G843" t="inlineStr"/>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -37194,6 +37886,9 @@
           <t>Cho EH</t>
         </is>
       </c>
+      <c r="E844" t="inlineStr"/>
+      <c r="F844" t="inlineStr"/>
+      <c r="G844" t="inlineStr"/>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -37216,6 +37911,9 @@
           <t>Shin SS</t>
         </is>
       </c>
+      <c r="E845" t="inlineStr"/>
+      <c r="F845" t="inlineStr"/>
+      <c r="G845" t="inlineStr"/>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -37238,6 +37936,9 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E846" t="inlineStr"/>
+      <c r="F846" t="inlineStr"/>
+      <c r="G846" t="inlineStr"/>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -37260,6 +37961,7 @@
           <t>Park YS</t>
         </is>
       </c>
+      <c r="E847" t="inlineStr"/>
       <c r="F847" t="inlineStr">
         <is>
           <t>Division of HIV and TB Control, Korea Centers for Disease Control and Prevention, Cheongwon, Korea.</t>
@@ -37292,6 +37994,9 @@
           <t>Hong SJ</t>
         </is>
       </c>
+      <c r="E848" t="inlineStr"/>
+      <c r="F848" t="inlineStr"/>
+      <c r="G848" t="inlineStr"/>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -37314,6 +38019,9 @@
           <t>Boo YK</t>
         </is>
       </c>
+      <c r="E849" t="inlineStr"/>
+      <c r="F849" t="inlineStr"/>
+      <c r="G849" t="inlineStr"/>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -37336,6 +38044,9 @@
           <t>Hwang ES</t>
         </is>
       </c>
+      <c r="E850" t="inlineStr"/>
+      <c r="F850" t="inlineStr"/>
+      <c r="G850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -37358,6 +38069,9 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E851" t="inlineStr"/>
+      <c r="F851" t="inlineStr"/>
+      <c r="G851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -37380,6 +38094,9 @@
           <t>Cho SH</t>
         </is>
       </c>
+      <c r="E852" t="inlineStr"/>
+      <c r="F852" t="inlineStr"/>
+      <c r="G852" t="inlineStr"/>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -37402,6 +38119,9 @@
           <t>Na KI</t>
         </is>
       </c>
+      <c r="E853" t="inlineStr"/>
+      <c r="F853" t="inlineStr"/>
+      <c r="G853" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -37424,6 +38144,9 @@
           <t>Cho EH</t>
         </is>
       </c>
+      <c r="E854" t="inlineStr"/>
+      <c r="F854" t="inlineStr"/>
+      <c r="G854" t="inlineStr"/>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -37446,6 +38169,9 @@
           <t>Shin SS</t>
         </is>
       </c>
+      <c r="E855" t="inlineStr"/>
+      <c r="F855" t="inlineStr"/>
+      <c r="G855" t="inlineStr"/>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -37468,6 +38194,7 @@
           <t>Hong SJ</t>
         </is>
       </c>
+      <c r="E856" t="inlineStr"/>
       <c r="F856" t="inlineStr">
         <is>
           <t>Division of HIV and TB Control, Korea Centers for Disease Control and Prevention, Seoul, Korea.</t>
@@ -37500,6 +38227,9 @@
           <t>Park YS</t>
         </is>
       </c>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr"/>
+      <c r="G857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -37522,6 +38252,9 @@
           <t>An H</t>
         </is>
       </c>
+      <c r="E858" t="inlineStr"/>
+      <c r="F858" t="inlineStr"/>
+      <c r="G858" t="inlineStr"/>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -37544,6 +38277,9 @@
           <t>Kang SM</t>
         </is>
       </c>
+      <c r="E859" t="inlineStr"/>
+      <c r="F859" t="inlineStr"/>
+      <c r="G859" t="inlineStr"/>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -37566,6 +38302,9 @@
           <t>Cho EH</t>
         </is>
       </c>
+      <c r="E860" t="inlineStr"/>
+      <c r="F860" t="inlineStr"/>
+      <c r="G860" t="inlineStr"/>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -37588,6 +38327,9 @@
           <t>Shin SS</t>
         </is>
       </c>
+      <c r="E861" t="inlineStr"/>
+      <c r="F861" t="inlineStr"/>
+      <c r="G861" t="inlineStr"/>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -37610,6 +38352,7 @@
           <t>Jeong I</t>
         </is>
       </c>
+      <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
           <t>Department of Internal Medicine, National Medical Center, Seoul, Korea.</t>
@@ -37642,6 +38385,9 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E863" t="inlineStr"/>
+      <c r="F863" t="inlineStr"/>
+      <c r="G863" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -37664,6 +38410,9 @@
           <t>Kim J</t>
         </is>
       </c>
+      <c r="E864" t="inlineStr"/>
+      <c r="F864" t="inlineStr"/>
+      <c r="G864" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -37686,6 +38435,9 @@
           <t>Oh SY</t>
         </is>
       </c>
+      <c r="E865" t="inlineStr"/>
+      <c r="F865" t="inlineStr"/>
+      <c r="G865" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -37708,6 +38460,9 @@
           <t>Lee JB</t>
         </is>
       </c>
+      <c r="E866" t="inlineStr"/>
+      <c r="F866" t="inlineStr"/>
+      <c r="G866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -37730,6 +38485,9 @@
           <t>Bai JY</t>
         </is>
       </c>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr"/>
+      <c r="G867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -37752,6 +38510,9 @@
           <t>Lee CH</t>
         </is>
       </c>
+      <c r="E868" t="inlineStr"/>
+      <c r="F868" t="inlineStr"/>
+      <c r="G868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -37774,6 +38535,7 @@
           <t>Manangan LP</t>
         </is>
       </c>
+      <c r="E869" t="inlineStr"/>
       <c r="F869" t="inlineStr">
         <is>
           <t>Division of Tuberculosis Elimination, National Center for HIV/AIDS, Viral Hepatitis, STD, and TB Prevention, Centers for Disease Control and Prevention (CDC), Atlanta, GA 30333, USA. lpm2@cdc.gov</t>
@@ -37806,6 +38568,9 @@
           <t>Salibay CJ</t>
         </is>
       </c>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr"/>
+      <c r="G870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -37828,6 +38593,9 @@
           <t>Wallace RM</t>
         </is>
       </c>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr"/>
+      <c r="G871" t="inlineStr"/>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -37850,6 +38618,9 @@
           <t>Kammerer S</t>
         </is>
       </c>
+      <c r="E872" t="inlineStr"/>
+      <c r="F872" t="inlineStr"/>
+      <c r="G872" t="inlineStr"/>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -37872,6 +38643,9 @@
           <t>Pratt R</t>
         </is>
       </c>
+      <c r="E873" t="inlineStr"/>
+      <c r="F873" t="inlineStr"/>
+      <c r="G873" t="inlineStr"/>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -37894,6 +38668,9 @@
           <t>McAllister L</t>
         </is>
       </c>
+      <c r="E874" t="inlineStr"/>
+      <c r="F874" t="inlineStr"/>
+      <c r="G874" t="inlineStr"/>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -37916,6 +38693,9 @@
           <t>Robison V</t>
         </is>
       </c>
+      <c r="E875" t="inlineStr"/>
+      <c r="F875" t="inlineStr"/>
+      <c r="G875" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -37938,6 +38718,7 @@
           <t>Lew WJ</t>
         </is>
       </c>
+      <c r="E876" t="inlineStr"/>
       <c r="F876" t="inlineStr">
         <is>
           <t>Korean Institute of Tuberculosis, Korean National Tuberculosis Association, Seoul, Korea. wjlew@hanmail.net</t>
@@ -37970,6 +38751,9 @@
           <t>Lee EG</t>
         </is>
       </c>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr"/>
+      <c r="G877" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -37992,6 +38776,9 @@
           <t>Bai JY</t>
         </is>
       </c>
+      <c r="E878" t="inlineStr"/>
+      <c r="F878" t="inlineStr"/>
+      <c r="G878" t="inlineStr"/>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -38014,6 +38801,9 @@
           <t>Kim HJ</t>
         </is>
       </c>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr"/>
+      <c r="G879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -38036,6 +38826,9 @@
           <t>Bai GH</t>
         </is>
       </c>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
+      <c r="G880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -38058,6 +38851,9 @@
           <t>Ahn DI</t>
         </is>
       </c>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr"/>
+      <c r="G881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -38080,6 +38876,9 @@
           <t>Lee JK</t>
         </is>
       </c>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr"/>
+      <c r="G882" t="inlineStr"/>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -38102,6 +38901,9 @@
           <t>Kim SJ</t>
         </is>
       </c>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr"/>
+      <c r="G883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -38124,6 +38926,7 @@
           <t>Li G</t>
         </is>
       </c>
+      <c r="E884" t="inlineStr"/>
       <c r="F884" t="inlineStr">
         <is>
           <t>Institute of Tuberculosis Control, Hubei Provincial Academy of Medical Sciences, Wuhan 430079, China.</t>
@@ -38156,6 +38959,9 @@
           <t>Wu X</t>
         </is>
       </c>
+      <c r="E885" t="inlineStr"/>
+      <c r="F885" t="inlineStr"/>
+      <c r="G885" t="inlineStr"/>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -38178,6 +38984,9 @@
           <t>Zhang T</t>
         </is>
       </c>
+      <c r="E886" t="inlineStr"/>
+      <c r="F886" t="inlineStr"/>
+      <c r="G886" t="inlineStr"/>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -38200,6 +39009,9 @@
           <t>Zhou L</t>
         </is>
       </c>
+      <c r="E887" t="inlineStr"/>
+      <c r="F887" t="inlineStr"/>
+      <c r="G887" t="inlineStr"/>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -38222,6 +39034,9 @@
           <t>Li K</t>
         </is>
       </c>
+      <c r="E888" t="inlineStr"/>
+      <c r="F888" t="inlineStr"/>
+      <c r="G888" t="inlineStr"/>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -38244,6 +39059,9 @@
           <t>Liu X</t>
         </is>
       </c>
+      <c r="E889" t="inlineStr"/>
+      <c r="F889" t="inlineStr"/>
+      <c r="G889" t="inlineStr"/>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -38266,6 +39084,9 @@
           <t>Li A</t>
         </is>
       </c>
+      <c r="E890" t="inlineStr"/>
+      <c r="F890" t="inlineStr"/>
+      <c r="G890" t="inlineStr"/>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -38288,6 +39109,9 @@
           <t>Dai X</t>
         </is>
       </c>
+      <c r="E891" t="inlineStr"/>
+      <c r="F891" t="inlineStr"/>
+      <c r="G891" t="inlineStr"/>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -38310,6 +39134,9 @@
           <t>Yuan F</t>
         </is>
       </c>
+      <c r="E892" t="inlineStr"/>
+      <c r="F892" t="inlineStr"/>
+      <c r="G892" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G892"/>
@@ -38387,6 +39214,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>확인ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>연구자키</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>논문수</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ORCID</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PMID</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>대상 연구자키</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>판정자</t>
+        </is>
+      </c>
+      <c r="L1" s="7" t="inlineStr">
+        <is>
+          <t>판정일</t>
+        </is>
+      </c>
+      <c r="M1" s="7" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ORCID여러개:youngjoonpark</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>youngjoonpark</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Young-Joon Park</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>ORCID 2개 — 기관 계열이 겹쳐 한 사람으로 묶음</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>질병관리본부 · 질병관리청</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0000-0001-9697-4173, 0000-0002-5971-7829</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>41982870, 41414825, 41334571, 41334527, 41333079, 41333694, 39048302, 33169559, 32610836</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="6" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>기관여러곳:honghyokkim</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>honghyokkim</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Honghyok Kim</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ORCID 없음 · 기관 계열 2곳 (Yale University / 고려대학교)</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Yale University · 고려대학교</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>35277170, 32164052</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="6" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>기관여러곳:wonseopark</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>wonseopark</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wonseo Park</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>ORCID 없음 · 기관 계열 2곳 (부산대학교 / 질병관리청)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>부산대학교병원 · 질병관리본부</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>33797276, 27812491</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORCID오류:heesunkim:0000-0002-0128-2789</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>heesunkim</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hee-Sun Kim</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>PubMed ORCID 오류 — Hee Jin Kim의 ORCID가 함께 붙음 (자동 무시)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0000-0002-0128-2789</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>37583964</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>같은 사람</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>자동</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>판정 불필요 — 기록용</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M5"/>
+  <dataValidations count="1">
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"같은 사람,다른 사람"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -38467,13 +39578,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -38486,7 +39597,9 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -38536,7 +39649,9 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -38583,6 +39698,44 @@
       <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">  이 시트는 다시 수집해도 지워지지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>'연구자확인' 시트: 동명이인일 수 있는 연구자 목록 (python paper_db.py check · fetch 때 자동으로 채움).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  사유: ORCID 2개 이상 · 기관 계열 2곳 이상인데 ORCID 없음 · 이니셜 이름 · PubMed ORCID 오류(자동 처리, 기록만).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  '판정' 칸(주황 머리글)에 같은 사람 / 다른 사람 을 고른다. 비어 있으면 '대기'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  다른 사람 → 다음 빌드부터 ORCID(없으면 기관 계열)별로 나눈다. 이니셜 이름에 같은 사람 → '대상 연구자키'로 합친다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  판정한 줄은 다시 채워도 그대로 남는다. 대상에서 빠지면 메모에 '(해당 없음)'이 붙는다.</t>
         </is>
       </c>
     </row>

--- a/논문DB.xlsx
+++ b/논문DB.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'논문'!$A$1:$Q$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'저자'!$A$1:$G$892</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'연구자확인'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'연구자확인'!$A$1:$M$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39214,7 +39214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -39317,7 +39317,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>ORCID 2개 — 기관 계열이 겹쳐 한 사람으로 묶음</t>
+          <t>ORCID 2개 — 기관 계열이 겹쳐 한 사람으로 묶음 — Young-Joon Park(…7829) / Youngjoon Park(ORCID 없음) / Young Joon Park(…4173)</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -39429,60 +39429,105 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>표기근거없음:jiyeonlee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>jiyeonlee</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ji Yeon Lee</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>표기 차이로 합쳤지만 ORCID·기관 계열이 안 겹침 — Ji Yeon Lee(국립중앙의료원) / Jiyeon Lee(질병관리청)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>국립중앙의료원 · 질병관리청</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0000-0002-7026-8235</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>41018774, 39595721, 41333694</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>ORCID오류:heesunkim:0000-0002-0128-2789</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>heesunkim</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Hee-Sun Kim</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>PubMed ORCID 오류 — Hee Jin Kim의 ORCID가 함께 붙음 (자동 무시)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>0000-0002-0128-2789</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>37583964</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>같은 사람</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>자동</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>판정 불필요 — 기록용</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M6"/>
   <dataValidations count="1">
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"같은 사람,다른 사람"</formula1>
@@ -39714,7 +39759,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  사유: ORCID 2개 이상 · 기관 계열 2곳 이상인데 ORCID 없음 · 이니셜 이름 · PubMed ORCID 오류(자동 처리, 기록만).</t>
+          <t xml:space="preserve">  사유: ORCID 2개 이상 · 기관 계열 2곳 이상인데 ORCID 없음 · 표기 차이로 합쳤지만 ORCID·기관 근거 없음 · 이니셜 이름 · PubMed ORCID 오류(자동 처리, 기록만).</t>
         </is>
       </c>
     </row>

--- a/논문DB.xlsx
+++ b/논문DB.xlsx
@@ -39302,40 +39302,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORCID여러개:youngjoonpark</t>
+          <t>기관여러곳:honghyokkim</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>youngjoonpark</t>
+          <t>honghyokkim</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Young-Joon Park</t>
+          <t>Honghyok Kim</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>ORCID 2개 — 기관 계열이 겹쳐 한 사람으로 묶음 — Young-Joon Park(…7829) / Youngjoon Park(ORCID 없음) / Young Joon Park(…4173)</t>
+          <t>ORCID 없음 · 기관 계열 2곳 (Yale University / 고려대학교)</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>질병관리본부 · 질병관리청</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0000-0001-9697-4173, 0000-0002-5971-7829</t>
-        </is>
-      </c>
+          <t>Yale University · 고려대학교</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>41982870, 41414825, 41334571, 41334527, 41333079, 41333694, 39048302, 33169559, 32610836</t>
+          <t>35277170, 32164052</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -39347,22 +39343,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기관여러곳:honghyokkim</t>
+          <t>기관여러곳:wonseopark</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>honghyokkim</t>
+          <t>wonseopark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Honghyok Kim</t>
+          <t>Wonseo Park</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ORCID 없음 · 기관 계열 2곳 (Yale University / 고려대학교)</t>
+          <t>ORCID 없음 · 기관 계열 2곳 (부산대학교 / 질병관리청)</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -39370,13 +39366,13 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Yale University · 고려대학교</t>
+          <t>부산대학교병원 · 질병관리본부</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>35277170, 32164052</t>
+          <t>33797276, 27812491</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -39388,39 +39384,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기관여러곳:wonseopark</t>
+          <t>나뉨:jiyeonlee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>wonseopark</t>
+          <t>jiyeonlee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wonseo Park</t>
+          <t>Ji Yeon Lee</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>ORCID 없음 · 기관 계열 2곳 (부산대학교 / 질병관리청)</t>
+          <t>이름이 비슷하지만 근거가 없어 2명으로 나눔 — ORCID·기관 계열이 안 겹침: Ji Yeon Lee(…8235 · 국립중앙의료원) / Jiyeon Lee(ORCID 없음 · 질병관리청)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>부산대학교병원 · 질병관리본부</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0000-0002-7026-8235</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>33797276, 27812491</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>39595721, 41018774, 41333694</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>jiyeonlee-8235, jiyeonlee-질병관리청</t>
+        </is>
+      </c>
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -39429,43 +39429,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>표기근거없음:jiyeonlee</t>
+          <t>나뉨:youngjoonpark</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>jiyeonlee</t>
+          <t>youngjoonpark</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ji Yeon Lee</t>
+          <t>Young-Joon Park</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>표기 차이로 합쳤지만 ORCID·기관 계열이 안 겹침 — Ji Yeon Lee(국립중앙의료원) / Jiyeon Lee(질병관리청)</t>
+          <t>이름이 비슷하지만 근거가 없어 2명으로 나눔 — ORCID가 서로 다름 (기관 계열은 같음): Young-Joon Park + Youngjoon Park(…7829 · 질병관리청) / Young Joon Park(…4173 · 질병관리본부 · 질병관리청) · 애매: Youngjoon Park(ORCID 없음)은 어느 쪽인지 불확실 — 지금은 youngjoonpark-7829 쪽</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>국립중앙의료원 · 질병관리청</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0000-0002-7026-8235</t>
+          <t>0000-0001-9697-4173, 0000-0002-5971-7829</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>41018774, 39595721, 41333694</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>32610836, 33169559, 39048302, 41333079, 41333694, 41334527, 41334571, 41414825, 41982870</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>youngjoonpark-4173, youngjoonpark-7829</t>
+        </is>
+      </c>
       <c r="J5" s="6" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
